--- a/odk/forms/crop_sown_registry_sown.xlsx
+++ b/odk/forms/crop_sown_registry_sown.xlsx
@@ -525,1837 +525,1877 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="29" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="29" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="29" t="inlineStr">
         <is>
           <t>label</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="29" t="inlineStr">
         <is>
           <t>hint</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="29" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="29" t="inlineStr">
         <is>
           <t>constraint</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="29" t="inlineStr">
         <is>
           <t>constraint_message</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="29" t="inlineStr">
         <is>
           <t>relevant</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="29" t="inlineStr">
         <is>
           <t>calculation</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="29" t="inlineStr">
         <is>
           <t>read_only</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="29" t="inlineStr">
         <is>
           <t>appearance</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="29" t="inlineStr">
         <is>
           <t>default</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="29" t="inlineStr">
         <is>
           <t>choice_filter</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="29" t="inlineStr">
         <is>
           <t>repeat_count</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="29" t="inlineStr">
         <is>
           <t>required_message</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="29" t="inlineStr">
         <is>
           <t>begin_group</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="29" t="inlineStr">
         <is>
           <t>farmer_identity</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="29" t="inlineStr">
         <is>
           <t>Farmer Identity</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" s="29" t="inlineStr">
         <is>
           <t>field-list</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="29" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="29" t="inlineStr">
         <is>
           <t>farmer_id</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="29" t="inlineStr">
         <is>
           <t>Farmer ID</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="29" t="inlineStr">
         <is>
           <t>FR- followed by 12 digits, for example FR-123456789012</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="29" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="29" t="inlineStr">
         <is>
           <t>regex(., '^FR-[0-9]{12}$')</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="29" t="inlineStr">
         <is>
           <t>The Farmer ID must be FR- followed by 12 digits, for example FR-123456789012.</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="O3" s="29" t="inlineStr">
         <is>
           <t>Enter the Farmer ID.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="29" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>fayda_id_entered</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="29" t="inlineStr">
         <is>
           <t>Fayda ID</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="29" t="inlineStr">
         <is>
           <t>The 16 digit FAN or the 12 digit FIN. Spaces are allowed.</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="29" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="29" t="inlineStr">
         <is>
           <t>regex(translate(., ' ', ''), '^([0-9]{12}|[0-9]{16})$')</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="29" t="inlineStr">
         <is>
           <t>The Fayda ID must be a 16 digit FAN or a 12 digit FIN. Spaces are allowed.</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="O4" s="29" t="inlineStr">
         <is>
           <t>Enter the Fayda ID.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="29" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>fayda_id</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="29" t="inlineStr">
         <is>
           <t>translate(${fayda_id_entered}, ' ', '')</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="29" t="inlineStr">
         <is>
           <t>end_group</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="29" t="inlineStr">
         <is>
           <t>begin_group</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>production_season_info</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="29" t="inlineStr">
         <is>
           <t>Production Season</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K7" s="29" t="inlineStr">
         <is>
           <t>field-list</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="29" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="29" t="inlineStr">
         <is>
           <t>crop_year</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="29" t="inlineStr">
         <is>
           <t>Crop Year</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="29" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="29" t="inlineStr">
         <is>
           <t>. = number(format-date(today(), '%Y'))</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="29" t="inlineStr">
         <is>
           <t>Only the current crop year is allowed.</t>
         </is>
       </c>
+      <c r="O8" s="29" t="inlineStr">
+        <is>
+          <t>Enter the crop year.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="29" t="inlineStr">
         <is>
           <t>select_one crop_season</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="29" t="inlineStr">
         <is>
           <t>production_season</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="29" t="inlineStr">
         <is>
           <t>Production Season</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="29" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="O9" s="29" t="inlineStr">
+        <is>
+          <t>Select the production season.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="29" t="inlineStr">
         <is>
           <t>end_group</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="29" t="inlineStr">
         <is>
           <t>begin_repeat</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="29" t="inlineStr">
         <is>
           <t>sowing_details</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="29" t="inlineStr">
         <is>
           <t>Sowing Details</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="29" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="29" t="inlineStr">
         <is>
           <t>land_info_id</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="29" t="inlineStr">
         <is>
           <t>Land ID</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="29" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="O12" s="29" t="inlineStr">
+        <is>
+          <t>Enter the Land ID.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="29" t="inlineStr">
         <is>
           <t>select_multiple cluster_status</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="29" t="inlineStr">
         <is>
           <t>cluster_status_ids</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Cluster / Non Cluster Status</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
+      <c r="C13" s="29" t="inlineStr">
+        <is>
+          <t>Cluster Status</t>
+        </is>
+      </c>
+      <c r="K13" s="29" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="29" t="inlineStr">
         <is>
           <t>begin_group</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="29" t="inlineStr">
         <is>
           <t>clustered_details</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="29" t="inlineStr">
         <is>
           <t>Clustered Details</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H14" s="29" t="inlineStr">
         <is>
           <t>selected(${cluster_status_ids}, 'clustered')</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="K14" s="29" t="inlineStr">
         <is>
           <t>field-list</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="29" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="29" t="inlineStr">
         <is>
           <t>cluster_name</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>FPC Name</t>
+      <c r="C15" s="29" t="inlineStr">
+        <is>
+          <t>Farmer Production Cluster (FPC) Name</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="29" t="inlineStr">
         <is>
           <t>select_one crop_season</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="29" t="inlineStr">
         <is>
           <t>cluster_season_id</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="29" t="inlineStr">
         <is>
           <t>Season</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F16" s="29" t="inlineStr">
         <is>
           <t>. = ${production_season}</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G16" s="29" t="inlineStr">
         <is>
           <t>Season must match the Production Season selected earlier.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="29" t="inlineStr">
         <is>
           <t>select_one agro_ecological_zone</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="29" t="inlineStr">
         <is>
           <t>cluster_agro_ecological_zone</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="29" t="inlineStr">
         <is>
           <t>Agro Ecological Zone</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="29" t="inlineStr">
         <is>
           <t>decimal</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="29" t="inlineStr">
         <is>
           <t>cluster_area_hectare</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="29" t="inlineStr">
         <is>
           <t>Total Cultivated Area (ha)</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F18" s="29" t="inlineStr">
         <is>
           <t>. &gt;= 0</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G18" s="29" t="inlineStr">
         <is>
           <t>Total Cultivated Area cannot be negative.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="29" t="inlineStr">
         <is>
           <t>select_one sowing_status</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="29" t="inlineStr">
         <is>
           <t>sowing_status</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="29" t="inlineStr">
         <is>
           <t>Sowing Status</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="29" t="inlineStr">
         <is>
           <t>decimal</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="29" t="inlineStr">
         <is>
           <t>cluster_area_sown</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Area Sown (ha) (Cluster)</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
+      <c r="C20" s="29" t="inlineStr">
+        <is>
+          <t>Area Sown (ha)</t>
+        </is>
+      </c>
+      <c r="F20" s="29" t="inlineStr">
         <is>
           <t>. &gt;= 0</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G20" s="29" t="inlineStr">
         <is>
           <t>Area Sown cannot be negative.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="29" t="inlineStr">
         <is>
           <t>select_multiple yes_only</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="29" t="inlineStr">
         <is>
           <t>cluster_has_pest_disease</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="29" t="inlineStr">
         <is>
           <t>Pest / Disease Occurrence</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="29" t="inlineStr">
         <is>
           <t>end_group</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="29" t="inlineStr">
         <is>
           <t>begin_group</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="29" t="inlineStr">
         <is>
           <t>independant_details</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="29" t="inlineStr">
         <is>
           <t>Independent Details</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H23" s="29" t="inlineStr">
         <is>
           <t>selected(${cluster_status_ids}, 'independent')</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="29" t="inlineStr">
         <is>
           <t>select_one crop_season</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="29" t="inlineStr">
         <is>
           <t>season_id</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="29" t="inlineStr">
         <is>
           <t>Season</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F24" s="29" t="inlineStr">
         <is>
           <t>. = ${production_season}</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G24" s="29" t="inlineStr">
         <is>
           <t>Season must match the Production Season selected earlier.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="29" t="inlineStr">
         <is>
           <t>decimal</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="29" t="inlineStr">
         <is>
           <t>area_sown</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="29" t="inlineStr">
         <is>
           <t>Area Sown (ha)</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F25" s="29" t="inlineStr">
         <is>
           <t>. &gt;= 0</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G25" s="29" t="inlineStr">
         <is>
           <t>Area Sown cannot be negative.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="29" t="inlineStr">
         <is>
           <t>select_one_from_file crop_name.csv</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="29" t="inlineStr">
         <is>
           <t>crop_name_id</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="29" t="inlineStr">
         <is>
           <t>Actual Crop Name</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E26" s="29" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="K26" s="29" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
+      <c r="O26" s="29" t="inlineStr">
+        <is>
+          <t>Select the actual crop name.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="29" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="29" t="inlineStr">
         <is>
           <t>sowing_date_gc</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Sowing Date (GC)</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
+      <c r="C27" s="29" t="inlineStr">
+        <is>
+          <t>Sowing Date (Gregorian calendar)</t>
+        </is>
+      </c>
+      <c r="F27" s="29" t="inlineStr">
         <is>
           <t>. &lt;= today()</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G27" s="29" t="inlineStr">
         <is>
           <t>Sowing Date cannot be in the future.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="29" t="inlineStr">
         <is>
           <t>select_one fertilizer_type</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="29" t="inlineStr">
         <is>
           <t>actual_fertilizer_type</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="29" t="inlineStr">
         <is>
           <t>Actual Fertilizer Type</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="K28" s="29" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="29" t="inlineStr">
         <is>
           <t>decimal</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="29" t="inlineStr">
         <is>
           <t>actual_fertilizer_qty</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="29" t="inlineStr">
         <is>
           <t>Actual Fertilizer Quantity (kg)</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F29" s="29" t="inlineStr">
         <is>
           <t>. &gt;= 0</t>
         </is>
       </c>
+      <c r="G29" s="29" t="inlineStr">
+        <is>
+          <t>Actual Fertilizer Quantity cannot be negative.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="29" t="inlineStr">
         <is>
           <t>select_multiple yes_only</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="29" t="inlineStr">
         <is>
           <t>has_pest_disease</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="29" t="inlineStr">
         <is>
           <t>Pest / Disease Occurrence</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="29" t="inlineStr">
         <is>
           <t>end_group</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="29" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="29" t="inlineStr">
         <is>
           <t>surveyor_name</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>DA Name</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
+      <c r="C32" s="29" t="inlineStr">
+        <is>
+          <t>Development Agent Name</t>
+        </is>
+      </c>
+      <c r="F32" s="29" t="inlineStr">
         <is>
           <t>regex(., '^[a-zA-Z\u1200-\u137F .\-]+$')</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>DA Name may contain only letters (English or Amharic), spaces, dots and hyphens</t>
+      <c r="G32" s="29" t="inlineStr">
+        <is>
+          <t>Enter the Development Agent's name using letters (English or Amharic), spaces, dots and hyphens only.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="29" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="29" t="inlineStr">
         <is>
           <t>surveyor_mobile_number</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>DA Mobile Number</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Format: 0911223344 or +251911223344</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
+      <c r="C33" s="29" t="inlineStr">
+        <is>
+          <t>Development Agent Mobile Number</t>
+        </is>
+      </c>
+      <c r="D33" s="29" t="inlineStr">
+        <is>
+          <t>For example 0911223344 or +251911223344</t>
+        </is>
+      </c>
+      <c r="F33" s="29" t="inlineStr">
         <is>
           <t>regex(., '^(\+251[79][0-9]{8}|0[79][0-9]{8})$')</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Enter valid Ethiopian number: 0911223344 or +251911223344</t>
+      <c r="G33" s="29" t="inlineStr">
+        <is>
+          <t>Enter a valid Ethiopian mobile number, for example 0911223344 or +251911223344.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="29" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="29" t="inlineStr">
         <is>
           <t>supervisor_name</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="29" t="inlineStr">
         <is>
           <t>Supervisor Name</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F34" s="29" t="inlineStr">
         <is>
           <t>regex(., '^[a-zA-Z\u1200-\u137F .\-]+$')</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Supervisor Name may contain only letters (English or Amharic), spaces, dots and hyphens</t>
+      <c r="G34" s="29" t="inlineStr">
+        <is>
+          <t>Enter the supervisor's name using letters (English or Amharic), spaces, dots and hyphens only.</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="29" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="29" t="inlineStr">
         <is>
           <t>supervisor_mobile_number</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="29" t="inlineStr">
         <is>
           <t>Supervisor Mobile Number</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Format: 0911223344 or +251911223344</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
+      <c r="D35" s="29" t="inlineStr">
+        <is>
+          <t>For example 0911223344 or +251911223344</t>
+        </is>
+      </c>
+      <c r="F35" s="29" t="inlineStr">
         <is>
           <t>regex(., '^(\+251[79][0-9]{8}|0[79][0-9]{8})$')</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Enter valid Ethiopian number: 0911223344 or +251911223344</t>
+      <c r="G35" s="29" t="inlineStr">
+        <is>
+          <t>Enter a valid Ethiopian mobile number, for example 0911223344 or +251911223344.</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="29" t="inlineStr">
         <is>
           <t>end_repeat</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="29" t="inlineStr">
         <is>
           <t>begin_repeat</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="29" t="inlineStr">
         <is>
           <t>infestation_incidents</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="29" t="inlineStr">
         <is>
           <t>Infestation Incidents</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="29" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="29" t="inlineStr">
         <is>
           <t>infestation_land_info_id</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="29" t="inlineStr">
         <is>
           <t>Land ID</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E38" s="29" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F38" s="29" t="inlineStr">
         <is>
           <t>selected(join(' ', ${land_info_id}), .)</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="G38" s="29" t="inlineStr">
         <is>
           <t>Land ID does not match the Land ID provided in Sowing Details. Please enter the correct Land ID.</t>
         </is>
       </c>
+      <c r="O38" s="29" t="inlineStr">
+        <is>
+          <t>Enter the Land ID.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="29" t="inlineStr">
         <is>
           <t>select_one cluster_status</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="29" t="inlineStr">
         <is>
           <t>cluster_status_id</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Cluster / Non Cluster Status</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
+      <c r="C39" s="29" t="inlineStr">
+        <is>
+          <t>Cluster Status</t>
+        </is>
+      </c>
+      <c r="K39" s="29" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="29" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="29" t="inlineStr">
         <is>
           <t>infestation_fpc_name</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>FPC Name</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
+      <c r="C40" s="29" t="inlineStr">
+        <is>
+          <t>Farmer Production Cluster (FPC) Name</t>
+        </is>
+      </c>
+      <c r="H40" s="29" t="inlineStr">
         <is>
           <t>selected(${cluster_status_id}, 'clustered')</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="29" t="inlineStr">
         <is>
           <t>select_one_from_file crop_name.csv</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="29" t="inlineStr">
         <is>
           <t>crop_name_id</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="29" t="inlineStr">
         <is>
           <t>Crop Type Affected</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E41" s="29" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="H41" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">selected(${cluster_status_id}, 'independent')
 </t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="K41" s="29" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
+      <c r="O41" s="29" t="inlineStr">
+        <is>
+          <t>Select the crop type affected.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="29" t="inlineStr">
         <is>
           <t>select_multiple infestation_type</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="29" t="inlineStr">
         <is>
           <t>infestation_type_ids</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="29" t="inlineStr">
         <is>
           <t>Type of Infestation</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="K42" s="29" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="29" t="inlineStr">
         <is>
           <t>select_one growth_stage</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="29" t="inlineStr">
         <is>
           <t>growth_stage</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="29" t="inlineStr">
         <is>
           <t>Growth Stage</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="K43" s="29" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="29" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="29" t="inlineStr">
         <is>
           <t>observation_date</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Date of Observation (GC)</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
+      <c r="C44" s="29" t="inlineStr">
+        <is>
+          <t>Date of Observation (Gregorian calendar)</t>
+        </is>
+      </c>
+      <c r="F44" s="29" t="inlineStr">
         <is>
           <t>. &lt;= today()</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G44" s="29" t="inlineStr">
         <is>
           <t>Date of Observation cannot be in the future.</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="29" t="inlineStr">
         <is>
           <t>note</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="29" t="inlineStr">
         <is>
           <t>ec_date_message</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>The selected date will be automatically converted to Ethiopian Calendar (EC) format.</t>
+      <c r="C45" s="29" t="inlineStr">
+        <is>
+          <t>The date you select is converted to the Ethiopian calendar automatically.</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="29" t="inlineStr">
         <is>
           <t>select_one security_level</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="29" t="inlineStr">
         <is>
           <t>security_level</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C46" s="29" t="inlineStr">
         <is>
           <t>Security Level</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="29" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="29" t="inlineStr">
         <is>
           <t>estimated_damage</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Estimated Crop Damage (%) or (ha)</t>
+      <c r="C47" s="29" t="inlineStr">
+        <is>
+          <t>Estimated Crop Damage (percent or hectares)</t>
+        </is>
+      </c>
+      <c r="D47" s="29" t="inlineStr">
+        <is>
+          <t>Write the amount followed by % or ha, for example 20% or 0.5 ha.</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="29" t="inlineStr">
         <is>
           <t>begin_group</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="29" t="inlineStr">
         <is>
           <t>pest_occurance</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C48" s="29" t="inlineStr">
         <is>
           <t>Pest Occurrence</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="H48" s="29" t="inlineStr">
         <is>
           <t>selected(${infestation_type_ids}, 'pest')</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="29" t="inlineStr">
         <is>
           <t>select_one pest_type</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="29" t="inlineStr">
         <is>
           <t>pest_type</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C49" s="29" t="inlineStr">
         <is>
           <t>Pest Type</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="K49" s="29" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="29" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="29" t="inlineStr">
         <is>
           <t>pest_name</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C50" s="29" t="inlineStr">
         <is>
           <t>Pest Name</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="29" t="inlineStr">
         <is>
           <t>select_one method_control</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="29" t="inlineStr">
         <is>
           <t>pest_pesticide_method</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" s="29" t="inlineStr">
         <is>
           <t>Method of Control (Pest)</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="K51" s="29" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="29" t="inlineStr">
         <is>
           <t>select_one pesticides_type</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="29" t="inlineStr">
         <is>
           <t>pesticide_type</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C52" s="29" t="inlineStr">
         <is>
           <t>Pesticide Type</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="K52" s="29" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="29" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B53" s="29" t="inlineStr">
         <is>
           <t>pesticide_name</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C53" s="29" t="inlineStr">
         <is>
           <t>Pesticide Name</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="A54" s="29" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B54" s="29" t="inlineStr">
         <is>
           <t>pest_frequency_of_application</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C54" s="29" t="inlineStr">
         <is>
           <t>Frequency of Application</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="A55" s="29" t="inlineStr">
         <is>
           <t>end_group</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="A56" s="29" t="inlineStr">
         <is>
           <t>begin_group</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B56" s="29" t="inlineStr">
         <is>
           <t>weed_occurrence</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C56" s="29" t="inlineStr">
         <is>
           <t>Weed Occurrence</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="H56" s="29" t="inlineStr">
         <is>
           <t>selected(${infestation_type_ids}, 'weed')</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="A57" s="29" t="inlineStr">
         <is>
           <t>select_one weed_type</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B57" s="29" t="inlineStr">
         <is>
           <t>weed_type</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C57" s="29" t="inlineStr">
         <is>
           <t>Weed Type</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="K57" s="29" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="A58" s="29" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B58" s="29" t="inlineStr">
         <is>
           <t>weed_name_id</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C58" s="29" t="inlineStr">
         <is>
           <t>Weed Name</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
+      <c r="A59" s="29" t="inlineStr">
         <is>
           <t>select_one method_control</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B59" s="29" t="inlineStr">
         <is>
           <t>weed_control_method</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C59" s="29" t="inlineStr">
         <is>
           <t>Method of Control (Weed)</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
+      <c r="K59" s="29" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="A60" s="29" t="inlineStr">
         <is>
           <t>select_one weedicides_type</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B60" s="29" t="inlineStr">
         <is>
           <t>weedicide_type</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Weedicides Type</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
+      <c r="C60" s="29" t="inlineStr">
+        <is>
+          <t>Weedicide Type</t>
+        </is>
+      </c>
+      <c r="K60" s="29" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="A61" s="29" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B61" s="29" t="inlineStr">
         <is>
           <t>weedicide_name</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Weedicides Name</t>
+      <c r="C61" s="29" t="inlineStr">
+        <is>
+          <t>Weedicide Name</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
+      <c r="A62" s="29" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B62" s="29" t="inlineStr">
         <is>
           <t>weed_frequency_of_application</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C62" s="29" t="inlineStr">
         <is>
           <t>Frequency of Application</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="A63" s="29" t="inlineStr">
         <is>
           <t>end_group</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="A64" s="29" t="inlineStr">
         <is>
           <t>begin_group</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B64" s="29" t="inlineStr">
         <is>
           <t>disease</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C64" s="29" t="inlineStr">
         <is>
           <t>Disease</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="H64" s="29" t="inlineStr">
         <is>
           <t>selected(${infestation_type_ids}, 'disease')</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
+      <c r="A65" s="29" t="inlineStr">
         <is>
           <t>select_one disease_type</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B65" s="29" t="inlineStr">
         <is>
           <t>disease_type</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C65" s="29" t="inlineStr">
         <is>
           <t>Disease Type</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
+      <c r="K65" s="29" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
+      <c r="A66" s="29" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B66" s="29" t="inlineStr">
         <is>
           <t>disease_name</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C66" s="29" t="inlineStr">
         <is>
           <t>Disease Name</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
+      <c r="A67" s="29" t="inlineStr">
         <is>
           <t>select_one method_control</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B67" s="29" t="inlineStr">
         <is>
           <t>ind_method_of_control</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C67" s="29" t="inlineStr">
         <is>
           <t>Method of Control (Disease)</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
+      <c r="K67" s="29" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
+      <c r="A68" s="29" t="inlineStr">
         <is>
           <t>select_one fungicide_type</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B68" s="29" t="inlineStr">
         <is>
           <t>fungicide_type</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C68" s="29" t="inlineStr">
         <is>
           <t>Fungicide / Bactericide Type</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
+      <c r="A69" s="29" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B69" s="29" t="inlineStr">
         <is>
           <t>fungicide_name</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C69" s="29" t="inlineStr">
         <is>
           <t>Fungicide / Bactericide Name</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
+      <c r="A70" s="29" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B70" s="29" t="inlineStr">
         <is>
           <t>disease_frequency_of_application</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C70" s="29" t="inlineStr">
         <is>
           <t>Frequency of Application</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
+      <c r="A71" s="29" t="inlineStr">
         <is>
           <t>end_group</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
+      <c r="A72" s="29" t="inlineStr">
         <is>
           <t>begin_group</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B72" s="29" t="inlineStr">
         <is>
           <t>nutrient_deficiency</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="C72" s="29" t="inlineStr">
         <is>
           <t>Nutrient Deficiency</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="H72" s="29" t="inlineStr">
         <is>
           <t>selected(${infestation_type_ids}, 'nutrient_deficiency')</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
+      <c r="A73" s="29" t="inlineStr">
         <is>
           <t>select_one nutrient_type</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B73" s="29" t="inlineStr">
         <is>
           <t>nutrient_type</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="C73" s="29" t="inlineStr">
         <is>
           <t>Nutrient Type</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
+      <c r="K73" s="29" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
+      <c r="A74" s="29" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B74" s="29" t="inlineStr">
         <is>
           <t>nutrient_name</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="C74" s="29" t="inlineStr">
         <is>
           <t>Nutrient Name</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
+      <c r="A75" s="29" t="inlineStr">
         <is>
           <t>select_one method_of_control</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B75" s="29" t="inlineStr">
         <is>
           <t>method_of_control</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C75" s="29" t="inlineStr">
         <is>
           <t>Method of Control (Nutrient)</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
+      <c r="K75" s="29" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
+      <c r="A76" s="29" t="inlineStr">
         <is>
           <t>select_one fert_type</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B76" s="29" t="inlineStr">
         <is>
           <t>fertilizer_type</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="C76" s="29" t="inlineStr">
         <is>
           <t>Fertilizer / Amendment Type</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
+      <c r="K76" s="29" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
+      <c r="A77" s="29" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B77" s="29" t="inlineStr">
         <is>
           <t>fertilizer_name</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C77" s="29" t="inlineStr">
         <is>
           <t>Fertilizer / Amendment Name</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
+      <c r="A78" s="29" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B78" s="29" t="inlineStr">
         <is>
           <t>nutrient_frequency_of_application</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="C78" s="29" t="inlineStr">
         <is>
           <t>Frequency of Application</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
+      <c r="A79" s="29" t="inlineStr">
         <is>
           <t>end_group</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
+      <c r="A80" s="29" t="inlineStr">
         <is>
           <t>begin_group</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B80" s="29" t="inlineStr">
         <is>
           <t>climate_shock</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="C80" s="29" t="inlineStr">
         <is>
           <t>Climate Shock</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="H80" s="29" t="inlineStr">
         <is>
           <t>selected(${infestation_type_ids}, 'climate_shock')</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
+      <c r="A81" s="29" t="inlineStr">
         <is>
           <t>select_one shock_type</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="B81" s="29" t="inlineStr">
         <is>
           <t>shock_type</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="C81" s="29" t="inlineStr">
         <is>
           <t>Shock Type</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
+      <c r="K81" s="29" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
+      <c r="A82" s="29" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B82" s="29" t="inlineStr">
         <is>
           <t>shock_event_name</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="C82" s="29" t="inlineStr">
         <is>
           <t>Shock Event Name / Description</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
+      <c r="A83" s="29" t="inlineStr">
         <is>
           <t>select_one m_control</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="B83" s="29" t="inlineStr">
         <is>
           <t>climate_method_of_control</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
+      <c r="C83" s="29" t="inlineStr">
         <is>
           <t>Method of Control (Climate)</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
+      <c r="K83" s="29" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
+      <c r="A84" s="29" t="inlineStr">
         <is>
           <t>select_one recovery_type</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="B84" s="29" t="inlineStr">
         <is>
           <t>recovery_input_type</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
+      <c r="C84" s="29" t="inlineStr">
         <is>
           <t>Recovery Input Type</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr">
+      <c r="K84" s="29" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
+      <c r="A85" s="29" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B85" s="29" t="inlineStr">
         <is>
           <t>recovery_input_name</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="C85" s="29" t="inlineStr">
         <is>
           <t>Recovery Input Name</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
+      <c r="A86" s="29" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="B86" s="29" t="inlineStr">
         <is>
           <t>recovery_frequency_of_application</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
+      <c r="C86" s="29" t="inlineStr">
         <is>
           <t>Frequency of Application</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
+      <c r="A87" s="29" t="inlineStr">
         <is>
           <t>end_group</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
+      <c r="A88" s="29" t="inlineStr">
         <is>
           <t>end_repeat</t>
         </is>
@@ -2376,2383 +2416,2383 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="29" t="inlineStr">
         <is>
           <t>list_name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="29" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="29" t="inlineStr">
         <is>
           <t>label</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="29" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="29" t="inlineStr">
         <is>
           <t>fert_type</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="29" t="inlineStr">
         <is>
           <t>pest_name</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="29" t="inlineStr">
         <is>
           <t>weed_name</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="29" t="inlineStr">
         <is>
           <t>infestation_type</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="29" t="inlineStr">
         <is>
           <t>pest</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="29" t="inlineStr">
         <is>
           <t>Pest (ተባይ)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="29" t="inlineStr">
         <is>
           <t>infestation_type</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="29" t="inlineStr">
         <is>
           <t>weed</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="29" t="inlineStr">
         <is>
           <t>Weed</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="29" t="inlineStr">
         <is>
           <t>infestation_type</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>disease</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="29" t="inlineStr">
         <is>
           <t>Disease (በሽታ)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="29" t="inlineStr">
         <is>
           <t>infestation_type</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>nutrient_deficiency</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="29" t="inlineStr">
         <is>
           <t>Nutrient Deficiency (የንጥረ ነገር እጥረት)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="29" t="inlineStr">
         <is>
           <t>infestation_type</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>climate_shock</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="29" t="inlineStr">
         <is>
           <t>Climate Shock</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="29" t="inlineStr">
         <is>
           <t>growth_stage</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>emergence</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="29" t="inlineStr">
         <is>
           <t>Emergence</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="29" t="inlineStr">
         <is>
           <t>growth_stage</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="29" t="inlineStr">
         <is>
           <t>vegetative</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="29" t="inlineStr">
         <is>
           <t>Vegetative</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="29" t="inlineStr">
         <is>
           <t>growth_stage</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="29" t="inlineStr">
         <is>
           <t>flowering</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="29" t="inlineStr">
         <is>
           <t>Flowering</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="29" t="inlineStr">
         <is>
           <t>growth_stage</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="29" t="inlineStr">
         <is>
           <t>maturity</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="29" t="inlineStr">
         <is>
           <t>Maturity</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="29" t="inlineStr">
         <is>
           <t>security_level</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="29" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="29" t="inlineStr">
         <is>
           <t>Low (ቀላል)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="29" t="inlineStr">
         <is>
           <t>security_level</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="29" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="29" t="inlineStr">
         <is>
           <t>Medium (መካከለኛ)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="29" t="inlineStr">
         <is>
           <t>security_level</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="29" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="29" t="inlineStr">
         <is>
           <t>High (ከፍተኛ)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="29" t="inlineStr">
         <is>
           <t>method_control</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="29" t="inlineStr">
         <is>
           <t>chemical_spray</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="29" t="inlineStr">
         <is>
           <t>Chemical Spray</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="29" t="inlineStr">
         <is>
           <t>method_control</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="29" t="inlineStr">
         <is>
           <t>hand_picking</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="29" t="inlineStr">
         <is>
           <t>Hand Picking</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="29" t="inlineStr">
         <is>
           <t>method_control</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="29" t="inlineStr">
         <is>
           <t>early_harvesting</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="29" t="inlineStr">
         <is>
           <t>Early Harvesting</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="29" t="inlineStr">
         <is>
           <t>nutrient_type</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="29" t="inlineStr">
         <is>
           <t>macronutrient</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="29" t="inlineStr">
         <is>
           <t>Macronutrient</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="29" t="inlineStr">
         <is>
           <t>nutrient_type</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="29" t="inlineStr">
         <is>
           <t>secondary_nutrient</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="29" t="inlineStr">
         <is>
           <t>Secondary Nutrient</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="29" t="inlineStr">
         <is>
           <t>nutrient_type</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="29" t="inlineStr">
         <is>
           <t>micronutrient</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="29" t="inlineStr">
         <is>
           <t>Micronutrient</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="29" t="inlineStr">
         <is>
           <t>method_of_control</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="29" t="inlineStr">
         <is>
           <t>soil_application</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="29" t="inlineStr">
         <is>
           <t>Soil Application</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="29" t="inlineStr">
         <is>
           <t>method_of_control</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="29" t="inlineStr">
         <is>
           <t>foliar_spray</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="29" t="inlineStr">
         <is>
           <t>Foliar Spray</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="29" t="inlineStr">
         <is>
           <t>method_of_control</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="29" t="inlineStr">
         <is>
           <t>organic_amendment</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="29" t="inlineStr">
         <is>
           <t>Organic Amendment</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="29" t="inlineStr">
         <is>
           <t>method_of_control</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="29" t="inlineStr">
         <is>
           <t>cultural</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Cultural (e.g. Liming, Crop Rotation)</t>
+      <c r="C23" s="29" t="inlineStr">
+        <is>
+          <t>Cultural (for example liming or crop rotation)</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="29" t="inlineStr">
         <is>
           <t>fert_type</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="29" t="inlineStr">
         <is>
           <t>organic</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="29" t="inlineStr">
         <is>
           <t>Organic</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="29" t="inlineStr">
         <is>
           <t>fert_type</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="29" t="inlineStr">
         <is>
           <t>inorganic</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="29" t="inlineStr">
         <is>
           <t>Inorganic</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="29" t="inlineStr">
         <is>
           <t>shock_type</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="29" t="inlineStr">
         <is>
           <t>frost</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="29" t="inlineStr">
         <is>
           <t>Frost</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="29" t="inlineStr">
         <is>
           <t>shock_type</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="29" t="inlineStr">
         <is>
           <t>flood</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="29" t="inlineStr">
         <is>
           <t>Flood</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="29" t="inlineStr">
         <is>
           <t>shock_type</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="29" t="inlineStr">
         <is>
           <t>hail</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="29" t="inlineStr">
         <is>
           <t>Hail</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="29" t="inlineStr">
         <is>
           <t>shock_type</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="29" t="inlineStr">
         <is>
           <t>drought</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="29" t="inlineStr">
         <is>
           <t>Drought</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="29" t="inlineStr">
         <is>
           <t>m_control</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="29" t="inlineStr">
         <is>
           <t>drainage</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="29" t="inlineStr">
         <is>
           <t>Drainage</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="29" t="inlineStr">
         <is>
           <t>m_control</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="29" t="inlineStr">
         <is>
           <t>irrigation</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="29" t="inlineStr">
         <is>
           <t>Irrigation</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="29" t="inlineStr">
         <is>
           <t>m_control</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="29" t="inlineStr">
         <is>
           <t>shelter_covering</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="29" t="inlineStr">
         <is>
           <t>Shelter / Covering</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="29" t="inlineStr">
         <is>
           <t>m_control</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="29" t="inlineStr">
         <is>
           <t>replanting</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="29" t="inlineStr">
         <is>
           <t>Replanting</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="29" t="inlineStr">
         <is>
           <t>m_control</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="29" t="inlineStr">
         <is>
           <t>windbreak</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="29" t="inlineStr">
         <is>
           <t>Windbreak</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="29" t="inlineStr">
         <is>
           <t>m_control</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="29" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="29" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="29" t="inlineStr">
         <is>
           <t>recovery_type</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="29" t="inlineStr">
         <is>
           <t>soil_conditioner</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="29" t="inlineStr">
         <is>
           <t>Soil Conditioner</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="29" t="inlineStr">
         <is>
           <t>recovery_type</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="29" t="inlineStr">
         <is>
           <t>replanting_material</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="29" t="inlineStr">
         <is>
           <t>Replanting Material</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="29" t="inlineStr">
         <is>
           <t>recovery_type</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="29" t="inlineStr">
         <is>
           <t>irrigation_equipment</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="29" t="inlineStr">
         <is>
           <t>Irrigation Equipment</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="29" t="inlineStr">
         <is>
           <t>recovery_type</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="29" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="29" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="29" t="inlineStr">
         <is>
           <t>yes_only</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="29" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="29" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="29" t="inlineStr">
         <is>
           <t>fertilizer_type</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="29" t="inlineStr">
         <is>
           <t>organic</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="29" t="inlineStr">
         <is>
           <t>Organic</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="29" t="inlineStr">
         <is>
           <t>fertilizer_type</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="29" t="inlineStr">
         <is>
           <t>inorganic</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="29" t="inlineStr">
         <is>
           <t>Inorganic</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="29" t="inlineStr">
         <is>
           <t>fertilizer_type</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="29" t="inlineStr">
         <is>
           <t>bio_fertilizer</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Bio Fertilizer</t>
+      <c r="C43" s="29" t="inlineStr">
+        <is>
+          <t>Bio-fertilizer</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="29" t="inlineStr">
         <is>
           <t>pest_type</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="29" t="inlineStr">
         <is>
           <t>aphids</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" s="29" t="inlineStr">
         <is>
           <t>Aphids</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="29" t="inlineStr">
         <is>
           <t>pest_type</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="29" t="inlineStr">
         <is>
           <t>whiteflies</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" s="29" t="inlineStr">
         <is>
           <t>Whiteflies</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="29" t="inlineStr">
         <is>
           <t>pest_type</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="29" t="inlineStr">
         <is>
           <t>thrips</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C46" s="29" t="inlineStr">
         <is>
           <t>Thrips</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="29" t="inlineStr">
         <is>
           <t>pest_type</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="29" t="inlineStr">
         <is>
           <t>stem_borer</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" s="29" t="inlineStr">
         <is>
           <t>Stem borer</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="29" t="inlineStr">
         <is>
           <t>pest_type</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="29" t="inlineStr">
         <is>
           <t>leaf_miner</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C48" s="29" t="inlineStr">
         <is>
           <t>Leaf miner</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="29" t="inlineStr">
         <is>
           <t>pest_type</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="29" t="inlineStr">
         <is>
           <t>armyworm</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C49" s="29" t="inlineStr">
         <is>
           <t>Armyworm</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="29" t="inlineStr">
         <is>
           <t>pest_type</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="29" t="inlineStr">
         <is>
           <t>cutworm</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C50" s="29" t="inlineStr">
         <is>
           <t>Cutworm</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="29" t="inlineStr">
         <is>
           <t>pest_type</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="29" t="inlineStr">
         <is>
           <t>bollworm</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" s="29" t="inlineStr">
         <is>
           <t>Bollworm</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="29" t="inlineStr">
         <is>
           <t>pest_type</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="29" t="inlineStr">
         <is>
           <t>beetles</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C52" s="29" t="inlineStr">
         <is>
           <t>Beetles</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="29" t="inlineStr">
         <is>
           <t>pest_type</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B53" s="29" t="inlineStr">
         <is>
           <t>mealybugs</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C53" s="29" t="inlineStr">
         <is>
           <t>Mealybugs</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="A54" s="29" t="inlineStr">
         <is>
           <t>pest_type</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B54" s="29" t="inlineStr">
         <is>
           <t>grasshoppers</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C54" s="29" t="inlineStr">
         <is>
           <t>Grasshoppers</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="A55" s="29" t="inlineStr">
         <is>
           <t>pest_type</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B55" s="29" t="inlineStr">
         <is>
           <t>leafhopper_(jassids)</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C55" s="29" t="inlineStr">
         <is>
           <t>Leafhopper (Jassids)</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="A56" s="29" t="inlineStr">
         <is>
           <t>pest_type</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B56" s="29" t="inlineStr">
         <is>
           <t>rats</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C56" s="29" t="inlineStr">
         <is>
           <t>Rats</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="A57" s="29" t="inlineStr">
         <is>
           <t>pest_type</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B57" s="29" t="inlineStr">
         <is>
           <t>field_mouse</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C57" s="29" t="inlineStr">
         <is>
           <t>Field mouse</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="A58" s="29" t="inlineStr">
         <is>
           <t>pest_type</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B58" s="29" t="inlineStr">
         <is>
           <t>snails</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C58" s="29" t="inlineStr">
         <is>
           <t>Snails</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
+      <c r="A59" s="29" t="inlineStr">
         <is>
           <t>pest_type</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B59" s="29" t="inlineStr">
         <is>
           <t>slugs</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C59" s="29" t="inlineStr">
         <is>
           <t>Slugs</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="A60" s="29" t="inlineStr">
         <is>
           <t>pest_type</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B60" s="29" t="inlineStr">
         <is>
           <t>leaf_spot</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C60" s="29" t="inlineStr">
         <is>
           <t>Leaf spot</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="A61" s="29" t="inlineStr">
         <is>
           <t>pest_type</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B61" s="29" t="inlineStr">
         <is>
           <t>powdery_mildew</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C61" s="29" t="inlineStr">
         <is>
           <t>Powdery mildew</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
+      <c r="A62" s="29" t="inlineStr">
         <is>
           <t>pest_type</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B62" s="29" t="inlineStr">
         <is>
           <t>downy_mildew</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C62" s="29" t="inlineStr">
         <is>
           <t>Downy mildew</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="A63" s="29" t="inlineStr">
         <is>
           <t>pest_type</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B63" s="29" t="inlineStr">
         <is>
           <t>rust</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C63" s="29" t="inlineStr">
         <is>
           <t>Rust</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="A64" s="29" t="inlineStr">
         <is>
           <t>pest_type</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B64" s="29" t="inlineStr">
         <is>
           <t>blight</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C64" s="29" t="inlineStr">
         <is>
           <t>Blight</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
+      <c r="A65" s="29" t="inlineStr">
         <is>
           <t>pest_type</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B65" s="29" t="inlineStr">
         <is>
           <t>wilt</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C65" s="29" t="inlineStr">
         <is>
           <t>Wilt</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
+      <c r="A66" s="29" t="inlineStr">
         <is>
           <t>pesticides_type</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B66" s="29" t="inlineStr">
         <is>
           <t>insecticide</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C66" s="29" t="inlineStr">
         <is>
           <t>Insecticide</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
+      <c r="A67" s="29" t="inlineStr">
         <is>
           <t>pesticides_type</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B67" s="29" t="inlineStr">
         <is>
           <t>fungicide</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C67" s="29" t="inlineStr">
         <is>
           <t>Fungicide</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
+      <c r="A68" s="29" t="inlineStr">
         <is>
           <t>pesticides_type</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B68" s="29" t="inlineStr">
         <is>
           <t>herbicide</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C68" s="29" t="inlineStr">
         <is>
           <t>Herbicide</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
+      <c r="A69" s="29" t="inlineStr">
         <is>
           <t>pesticides_type</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B69" s="29" t="inlineStr">
         <is>
           <t>rodenticide</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C69" s="29" t="inlineStr">
         <is>
           <t>Rodenticide</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
+      <c r="A70" s="29" t="inlineStr">
         <is>
           <t>pesticides_type</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B70" s="29" t="inlineStr">
         <is>
           <t>bactericide</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C70" s="29" t="inlineStr">
         <is>
           <t>Bactericide</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
+      <c r="A71" s="29" t="inlineStr">
         <is>
           <t>pesticides_type</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B71" s="29" t="inlineStr">
         <is>
           <t>nematicide</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="C71" s="29" t="inlineStr">
         <is>
           <t>Nematicide</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
+      <c r="A72" s="29" t="inlineStr">
         <is>
           <t>pesticides_type</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B72" s="29" t="inlineStr">
         <is>
           <t>acaricide_miticide</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="C72" s="29" t="inlineStr">
         <is>
           <t>Acaricide / Miticide</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
+      <c r="A73" s="29" t="inlineStr">
         <is>
           <t>pesticides_type</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B73" s="29" t="inlineStr">
         <is>
           <t>molluscicide</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="C73" s="29" t="inlineStr">
         <is>
           <t>Molluscicide</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
+      <c r="A74" s="29" t="inlineStr">
         <is>
           <t>pesticides_type</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B74" s="29" t="inlineStr">
         <is>
           <t>termiticide</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="C74" s="29" t="inlineStr">
         <is>
           <t>Termiticide</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
+      <c r="A75" s="29" t="inlineStr">
         <is>
           <t>pesticides_type</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B75" s="29" t="inlineStr">
         <is>
           <t>avicide</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C75" s="29" t="inlineStr">
         <is>
           <t>Avicide</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
+      <c r="A76" s="29" t="inlineStr">
         <is>
           <t>pesticides_type</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B76" s="29" t="inlineStr">
         <is>
           <t>piscicide</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="C76" s="29" t="inlineStr">
         <is>
           <t>Piscicide</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
+      <c r="A77" s="29" t="inlineStr">
         <is>
           <t>pesticides_type</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B77" s="29" t="inlineStr">
         <is>
           <t>algicide</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C77" s="29" t="inlineStr">
         <is>
           <t>Algicide</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
+      <c r="A78" s="29" t="inlineStr">
         <is>
           <t>pesticides_type</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B78" s="29" t="inlineStr">
         <is>
           <t>virucide</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="C78" s="29" t="inlineStr">
         <is>
           <t>Virucide</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
+      <c r="A79" s="29" t="inlineStr">
         <is>
           <t>weedicides_type</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B79" s="29" t="inlineStr">
         <is>
           <t>pre_emergent_herbicide</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C79" s="29" t="inlineStr">
         <is>
           <t>Pre-emergent Herbicide</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
+      <c r="A80" s="29" t="inlineStr">
         <is>
           <t>weedicides_type</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B80" s="29" t="inlineStr">
         <is>
           <t>post_emergent_herbicide</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="C80" s="29" t="inlineStr">
         <is>
           <t>Post-emergent Herbicide</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
+      <c r="A81" s="29" t="inlineStr">
         <is>
           <t>weedicides_type</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="B81" s="29" t="inlineStr">
         <is>
           <t>systemic_herbicide</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="C81" s="29" t="inlineStr">
         <is>
           <t>Systemic Herbicide</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
+      <c r="A82" s="29" t="inlineStr">
         <is>
           <t>weedicides_type</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B82" s="29" t="inlineStr">
         <is>
           <t>contact_herbicide</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="C82" s="29" t="inlineStr">
         <is>
           <t>Contact Herbicide</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
+      <c r="A83" s="29" t="inlineStr">
         <is>
           <t>weedicides_type</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="B83" s="29" t="inlineStr">
         <is>
           <t>graminicide</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
+      <c r="C83" s="29" t="inlineStr">
         <is>
           <t>Graminicide</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
+      <c r="A84" s="29" t="inlineStr">
         <is>
           <t>weedicides_type</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="B84" s="29" t="inlineStr">
         <is>
           <t>broadleaf_herbicide</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
+      <c r="C84" s="29" t="inlineStr">
         <is>
           <t>Broadleaf Herbicide</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
+      <c r="A85" s="29" t="inlineStr">
         <is>
           <t>weedicides_type</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B85" s="29" t="inlineStr">
         <is>
           <t>sedge_herbicide</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="C85" s="29" t="inlineStr">
         <is>
           <t>Sedge Herbicide</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
+      <c r="A86" s="29" t="inlineStr">
         <is>
           <t>weedicides_type</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="B86" s="29" t="inlineStr">
         <is>
           <t>aquatic_herbicide</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
+      <c r="C86" s="29" t="inlineStr">
         <is>
           <t>Aquatic Herbicide</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
+      <c r="A87" s="29" t="inlineStr">
         <is>
           <t>weedicides_type</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="B87" s="29" t="inlineStr">
         <is>
           <t>foliar_herbicide</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="C87" s="29" t="inlineStr">
         <is>
           <t>Foliar Herbicide</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
+      <c r="A88" s="29" t="inlineStr">
         <is>
           <t>weedicides_type</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B88" s="29" t="inlineStr">
         <is>
           <t>soil_herbicide</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="C88" s="29" t="inlineStr">
         <is>
           <t>Soil Herbicide</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
+      <c r="A89" s="29" t="inlineStr">
         <is>
           <t>weed_type</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="B89" s="29" t="inlineStr">
         <is>
           <t>annual_weed</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
+      <c r="C89" s="29" t="inlineStr">
         <is>
           <t>Annual weed</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
+      <c r="A90" s="29" t="inlineStr">
         <is>
           <t>weed_type</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="B90" s="29" t="inlineStr">
         <is>
           <t>biennial_weed</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
+      <c r="C90" s="29" t="inlineStr">
         <is>
           <t>Biennial weed</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
+      <c r="A91" s="29" t="inlineStr">
         <is>
           <t>weed_type</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="B91" s="29" t="inlineStr">
         <is>
           <t>perennial_weed</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
+      <c r="C91" s="29" t="inlineStr">
         <is>
           <t>Perennial weed</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
+      <c r="A92" s="29" t="inlineStr">
         <is>
           <t>weed_type</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="B92" s="29" t="inlineStr">
         <is>
           <t>kharif_summer</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
+      <c r="C92" s="29" t="inlineStr">
         <is>
           <t>Kharif / Summer</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
+      <c r="A93" s="29" t="inlineStr">
         <is>
           <t>weed_type</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="B93" s="29" t="inlineStr">
         <is>
           <t>rabi_winter</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
+      <c r="C93" s="29" t="inlineStr">
         <is>
           <t>Rabi / Winter</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
+      <c r="A94" s="29" t="inlineStr">
         <is>
           <t>weed_type</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
+      <c r="B94" s="29" t="inlineStr">
         <is>
           <t>year_round</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
+      <c r="C94" s="29" t="inlineStr">
         <is>
           <t>Year-round</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
+      <c r="A95" s="29" t="inlineStr">
         <is>
           <t>weed_type</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
+      <c r="B95" s="29" t="inlineStr">
         <is>
           <t>grassy</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
+      <c r="C95" s="29" t="inlineStr">
         <is>
           <t>Grassy</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
+      <c r="A96" s="29" t="inlineStr">
         <is>
           <t>weed_type</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
+      <c r="B96" s="29" t="inlineStr">
         <is>
           <t>sedge</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
+      <c r="C96" s="29" t="inlineStr">
         <is>
           <t>Sedge</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
+      <c r="A97" s="29" t="inlineStr">
         <is>
           <t>weed_type</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
+      <c r="B97" s="29" t="inlineStr">
         <is>
           <t>broadleaf</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
+      <c r="C97" s="29" t="inlineStr">
         <is>
           <t>Broadleaf</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
+      <c r="A98" s="29" t="inlineStr">
         <is>
           <t>weed_type</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
+      <c r="B98" s="29" t="inlineStr">
         <is>
           <t>aquatic</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
+      <c r="C98" s="29" t="inlineStr">
         <is>
           <t>Aquatic</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
+      <c r="A99" s="29" t="inlineStr">
         <is>
           <t>weed_type</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
+      <c r="B99" s="29" t="inlineStr">
         <is>
           <t>terrestrial</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
+      <c r="C99" s="29" t="inlineStr">
         <is>
           <t>Terrestrial</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
+      <c r="A100" s="29" t="inlineStr">
         <is>
           <t>weed_type</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
+      <c r="B100" s="29" t="inlineStr">
         <is>
           <t>parasitic</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr">
+      <c r="C100" s="29" t="inlineStr">
         <is>
           <t>Parasitic</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
+      <c r="A101" s="29" t="inlineStr">
         <is>
           <t>weed_type</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
+      <c r="B101" s="29" t="inlineStr">
         <is>
           <t>epiphytic</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
+      <c r="C101" s="29" t="inlineStr">
         <is>
           <t>Epiphytic</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr">
+      <c r="A102" s="29" t="inlineStr">
         <is>
           <t>weed_type</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
+      <c r="B102" s="29" t="inlineStr">
         <is>
           <t>noxious</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr">
+      <c r="C102" s="29" t="inlineStr">
         <is>
           <t>Noxious</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr">
+      <c r="A103" s="29" t="inlineStr">
         <is>
           <t>weed_type</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
+      <c r="B103" s="29" t="inlineStr">
         <is>
           <t>poisonous</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
+      <c r="C103" s="29" t="inlineStr">
         <is>
           <t>Poisonous</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr">
+      <c r="A104" s="29" t="inlineStr">
         <is>
           <t>weed_type</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
+      <c r="B104" s="29" t="inlineStr">
         <is>
           <t>allelopathic</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
+      <c r="C104" s="29" t="inlineStr">
         <is>
           <t>Allelopathic</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr">
+      <c r="A105" s="29" t="inlineStr">
         <is>
           <t>weed_type</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
+      <c r="B105" s="29" t="inlineStr">
         <is>
           <t>invasive</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
+      <c r="C105" s="29" t="inlineStr">
         <is>
           <t>Invasive</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr">
+      <c r="A106" s="29" t="inlineStr">
         <is>
           <t>weed_type</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
+      <c r="B106" s="29" t="inlineStr">
         <is>
           <t>climbing</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr">
+      <c r="C106" s="29" t="inlineStr">
         <is>
           <t>Climbing</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr">
+      <c r="A107" s="29" t="inlineStr">
         <is>
           <t>weed_type</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
+      <c r="B107" s="29" t="inlineStr">
         <is>
           <t>rosette</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr">
+      <c r="C107" s="29" t="inlineStr">
         <is>
           <t>Rosette</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr">
+      <c r="A108" s="29" t="inlineStr">
         <is>
           <t>weed_type</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
+      <c r="B108" s="29" t="inlineStr">
         <is>
           <t>creeping</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr">
+      <c r="C108" s="29" t="inlineStr">
         <is>
           <t>Creeping</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr">
+      <c r="A109" s="29" t="inlineStr">
         <is>
           <t>fertilizer_type</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
+      <c r="B109" s="29" t="inlineStr">
         <is>
           <t>nps</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Nps</t>
+      <c r="C109" s="29" t="inlineStr">
+        <is>
+          <t>NPS</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr">
+      <c r="A110" s="29" t="inlineStr">
         <is>
           <t>fertilizer_type</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr">
+      <c r="B110" s="29" t="inlineStr">
         <is>
           <t>npsb</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Npsb</t>
+      <c r="C110" s="29" t="inlineStr">
+        <is>
+          <t>NPSB</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr">
+      <c r="A111" s="29" t="inlineStr">
         <is>
           <t>fertilizer_type</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr">
+      <c r="B111" s="29" t="inlineStr">
         <is>
           <t>dap</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Dap</t>
+      <c r="C111" s="29" t="inlineStr">
+        <is>
+          <t>DAP</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr">
+      <c r="A112" s="29" t="inlineStr">
         <is>
           <t>fertilizer_type</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr">
+      <c r="B112" s="29" t="inlineStr">
         <is>
           <t>compost</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr">
+      <c r="C112" s="29" t="inlineStr">
         <is>
           <t>Compost</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr">
+      <c r="A113" s="29" t="inlineStr">
         <is>
           <t>fertilizer_type</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr">
+      <c r="B113" s="29" t="inlineStr">
         <is>
           <t>manure</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr">
+      <c r="C113" s="29" t="inlineStr">
         <is>
           <t>Manure</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr">
+      <c r="A114" s="29" t="inlineStr">
         <is>
           <t>fertilizer_type</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr">
+      <c r="B114" s="29" t="inlineStr">
         <is>
           <t>blended</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr">
+      <c r="C114" s="29" t="inlineStr">
         <is>
           <t>Blended</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr">
+      <c r="A115" s="29" t="inlineStr">
         <is>
           <t>fertilizer_type</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr">
+      <c r="B115" s="29" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr">
+      <c r="C115" s="29" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr">
+      <c r="A116" s="29" t="inlineStr">
         <is>
           <t>sowing_status</t>
         </is>
       </c>
-      <c r="B116" t="inlineStr">
+      <c r="B116" s="29" t="inlineStr">
         <is>
           <t>sown</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr">
+      <c r="C116" s="29" t="inlineStr">
         <is>
           <t>Sown</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr">
+      <c r="A117" s="29" t="inlineStr">
         <is>
           <t>sowing_status</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr">
+      <c r="B117" s="29" t="inlineStr">
         <is>
           <t>not_sown</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr">
+      <c r="C117" s="29" t="inlineStr">
         <is>
           <t>Not Sown</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr">
+      <c r="A118" s="29" t="inlineStr">
         <is>
           <t>cluster_status</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr">
+      <c r="B118" s="29" t="inlineStr">
         <is>
           <t>clustered</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr">
+      <c r="C118" s="29" t="inlineStr">
         <is>
           <t>Clustered</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr">
+      <c r="A119" s="29" t="inlineStr">
         <is>
           <t>cluster_status</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr">
+      <c r="B119" s="29" t="inlineStr">
         <is>
           <t>independent</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr">
+      <c r="C119" s="29" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr">
+      <c r="A120" s="29" t="inlineStr">
         <is>
           <t>disease_type</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr">
+      <c r="B120" s="29" t="inlineStr">
         <is>
           <t>leaf_spot</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr">
+      <c r="C120" s="29" t="inlineStr">
         <is>
           <t>Leaf spot</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="inlineStr">
+      <c r="A121" s="29" t="inlineStr">
         <is>
           <t>disease_type</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr">
+      <c r="B121" s="29" t="inlineStr">
         <is>
           <t>powdery_mildew</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr">
+      <c r="C121" s="29" t="inlineStr">
         <is>
           <t>Powdery mildew</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr">
+      <c r="A122" s="29" t="inlineStr">
         <is>
           <t>disease_type</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr">
+      <c r="B122" s="29" t="inlineStr">
         <is>
           <t>downy_mildew</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr">
+      <c r="C122" s="29" t="inlineStr">
         <is>
           <t>Downy mildew</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" t="inlineStr">
+      <c r="A123" s="29" t="inlineStr">
         <is>
           <t>disease_type</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr">
+      <c r="B123" s="29" t="inlineStr">
         <is>
           <t>rust</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr">
+      <c r="C123" s="29" t="inlineStr">
         <is>
           <t>Rust</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" t="inlineStr">
+      <c r="A124" s="29" t="inlineStr">
         <is>
           <t>disease_type</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr">
+      <c r="B124" s="29" t="inlineStr">
         <is>
           <t>blight</t>
         </is>
       </c>
-      <c r="C124" t="inlineStr">
+      <c r="C124" s="29" t="inlineStr">
         <is>
           <t>Blight</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="inlineStr">
+      <c r="A125" s="29" t="inlineStr">
         <is>
           <t>disease_type</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr">
+      <c r="B125" s="29" t="inlineStr">
         <is>
           <t>wilt</t>
         </is>
       </c>
-      <c r="C125" t="inlineStr">
+      <c r="C125" s="29" t="inlineStr">
         <is>
           <t>Wilt</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" t="inlineStr">
+      <c r="A126" s="29" t="inlineStr">
         <is>
           <t>disease_type</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr">
+      <c r="B126" s="29" t="inlineStr">
         <is>
           <t>mosaic_virus</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr">
+      <c r="C126" s="29" t="inlineStr">
         <is>
           <t>Mosaic virus</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr">
+      <c r="A127" s="29" t="inlineStr">
         <is>
           <t>disease_type</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr">
+      <c r="B127" s="29" t="inlineStr">
         <is>
           <t>smut</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr">
+      <c r="C127" s="29" t="inlineStr">
         <is>
           <t>Smut</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr">
+      <c r="A128" s="29" t="inlineStr">
         <is>
           <t>disease_type</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr">
+      <c r="B128" s="29" t="inlineStr">
         <is>
           <t>anthracnose</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr">
+      <c r="C128" s="29" t="inlineStr">
         <is>
           <t>Anthracnose</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="inlineStr">
+      <c r="A129" s="29" t="inlineStr">
         <is>
           <t>disease_type</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr">
+      <c r="B129" s="29" t="inlineStr">
         <is>
           <t>root_rot</t>
         </is>
       </c>
-      <c r="C129" t="inlineStr">
+      <c r="C129" s="29" t="inlineStr">
         <is>
           <t>Root rot</t>
         </is>
       </c>
     </row>
     <row r="130">
-      <c r="A130" t="inlineStr">
+      <c r="A130" s="29" t="inlineStr">
         <is>
           <t>fungicide_type</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr">
+      <c r="B130" s="29" t="inlineStr">
         <is>
           <t>fungicide</t>
         </is>
       </c>
-      <c r="C130" t="inlineStr">
+      <c r="C130" s="29" t="inlineStr">
         <is>
           <t>Fungicide</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="A131" t="inlineStr">
+      <c r="A131" s="29" t="inlineStr">
         <is>
           <t>fungicide_type</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr">
+      <c r="B131" s="29" t="inlineStr">
         <is>
           <t>bactericide</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr">
+      <c r="C131" s="29" t="inlineStr">
         <is>
           <t>Bactericide</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" t="inlineStr">
+      <c r="A132" s="29" t="inlineStr">
         <is>
           <t>crop_season</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr">
+      <c r="B132" s="29" t="inlineStr">
         <is>
           <t>SEASON_MEHER</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr">
+      <c r="C132" s="29" t="inlineStr">
         <is>
           <t>Meher (main rains)</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="inlineStr">
+      <c r="A133" s="29" t="inlineStr">
         <is>
           <t>crop_season</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr">
+      <c r="B133" s="29" t="inlineStr">
         <is>
           <t>SEASON_BELG</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr">
+      <c r="C133" s="29" t="inlineStr">
         <is>
           <t>Belg (short rains)</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="A134" t="inlineStr">
+      <c r="A134" s="29" t="inlineStr">
         <is>
           <t>crop_season</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr">
+      <c r="B134" s="29" t="inlineStr">
         <is>
           <t>SEASON_IRRIGATION</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr">
+      <c r="C134" s="29" t="inlineStr">
         <is>
           <t>Irrigation (dry season)</t>
         </is>
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="inlineStr">
+      <c r="A135" s="29" t="inlineStr">
         <is>
           <t>agro_ecological_zone</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr">
+      <c r="B135" s="29" t="inlineStr">
         <is>
           <t>AEZ_BEREHA</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr">
+      <c r="C135" s="29" t="inlineStr">
         <is>
           <t>Bereha (hot lowland)</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="A136" t="inlineStr">
+      <c r="A136" s="29" t="inlineStr">
         <is>
           <t>agro_ecological_zone</t>
         </is>
       </c>
-      <c r="B136" t="inlineStr">
+      <c r="B136" s="29" t="inlineStr">
         <is>
           <t>AEZ_KOLLA</t>
         </is>
       </c>
-      <c r="C136" t="inlineStr">
+      <c r="C136" s="29" t="inlineStr">
         <is>
           <t>Kolla (lowland)</t>
         </is>
       </c>
     </row>
     <row r="137">
-      <c r="A137" t="inlineStr">
+      <c r="A137" s="29" t="inlineStr">
         <is>
           <t>agro_ecological_zone</t>
         </is>
       </c>
-      <c r="B137" t="inlineStr">
+      <c r="B137" s="29" t="inlineStr">
         <is>
           <t>AEZ_WEYNA_DEGA</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr">
+      <c r="C137" s="29" t="inlineStr">
         <is>
           <t>Weyna Dega (midland)</t>
         </is>
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="inlineStr">
+      <c r="A138" s="29" t="inlineStr">
         <is>
           <t>agro_ecological_zone</t>
         </is>
       </c>
-      <c r="B138" t="inlineStr">
+      <c r="B138" s="29" t="inlineStr">
         <is>
           <t>AEZ_DEGA</t>
         </is>
       </c>
-      <c r="C138" t="inlineStr">
+      <c r="C138" s="29" t="inlineStr">
         <is>
           <t>Dega (highland)</t>
         </is>
       </c>
     </row>
     <row r="139">
-      <c r="A139" t="inlineStr">
+      <c r="A139" s="29" t="inlineStr">
         <is>
           <t>agro_ecological_zone</t>
         </is>
       </c>
-      <c r="B139" t="inlineStr">
+      <c r="B139" s="29" t="inlineStr">
         <is>
           <t>AEZ_WURCH</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr">
+      <c r="C139" s="29" t="inlineStr">
         <is>
           <t>Wurch (cold highland)</t>
         </is>
@@ -4773,64 +4813,64 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="29" t="inlineStr">
         <is>
           <t>form_title</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="29" t="inlineStr">
         <is>
           <t>form_id</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="29" t="inlineStr">
         <is>
           <t>version</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="29" t="inlineStr">
         <is>
           <t>default_language</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="29" t="inlineStr">
         <is>
           <t>style</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="29" t="inlineStr">
         <is>
           <t>allow_choice_duplicates</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>CSR – 3. Sowing</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
+      <c r="A2" s="29" t="inlineStr">
+        <is>
+          <t>Crop Sown Registry - 3. Sowing</t>
+        </is>
+      </c>
+      <c r="B2" s="29" t="inlineStr">
         <is>
           <t>crop_sown_registry_sown</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2026.10.30</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
+      <c r="C2" s="29" t="inlineStr">
+        <is>
+          <t>2026.10.31</t>
+        </is>
+      </c>
+      <c r="D2" s="29" t="inlineStr">
         <is>
           <t>English (en)</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="29" t="inlineStr">
         <is>
           <t>pages</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="29" t="inlineStr">
         <is>
           <t>yes</t>
         </is>

--- a/odk/forms/crop_sown_registry_sown.xlsx
+++ b/odk/forms/crop_sown_registry_sown.xlsx
@@ -4857,7 +4857,7 @@
       </c>
       <c r="C2" s="29" t="inlineStr">
         <is>
-          <t>2026.10.31</t>
+          <t>2026.10.31.1</t>
         </is>
       </c>
       <c r="D2" s="29" t="inlineStr">

--- a/odk/forms/crop_sown_registry_sown.xlsx
+++ b/odk/forms/crop_sown_registry_sown.xlsx
@@ -525,1877 +525,1877 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="29" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="B1" s="29" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C1" s="29" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>label</t>
         </is>
       </c>
-      <c r="D1" s="29" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>hint</t>
         </is>
       </c>
-      <c r="E1" s="29" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="F1" s="29" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>constraint</t>
         </is>
       </c>
-      <c r="G1" s="29" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>constraint_message</t>
         </is>
       </c>
-      <c r="H1" s="29" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>relevant</t>
         </is>
       </c>
-      <c r="I1" s="29" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>calculation</t>
         </is>
       </c>
-      <c r="J1" s="29" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>read_only</t>
         </is>
       </c>
-      <c r="K1" s="29" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>appearance</t>
         </is>
       </c>
-      <c r="L1" s="29" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>default</t>
         </is>
       </c>
-      <c r="M1" s="29" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>choice_filter</t>
         </is>
       </c>
-      <c r="N1" s="29" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>repeat_count</t>
         </is>
       </c>
-      <c r="O1" s="29" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>required_message</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="29" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>begin_group</t>
         </is>
       </c>
-      <c r="B2" s="29" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>farmer_identity</t>
         </is>
       </c>
-      <c r="C2" s="29" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Farmer Identity</t>
         </is>
       </c>
-      <c r="K2" s="29" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>field-list</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="29" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B3" s="29" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>farmer_id</t>
         </is>
       </c>
-      <c r="C3" s="29" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Farmer ID</t>
         </is>
       </c>
-      <c r="D3" s="29" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>FR- followed by 12 digits, for example FR-123456789012</t>
         </is>
       </c>
-      <c r="E3" s="29" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="F3" s="29" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>regex(., '^FR-[0-9]{12}$')</t>
         </is>
       </c>
-      <c r="G3" s="29" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>The Farmer ID must be FR- followed by 12 digits, for example FR-123456789012.</t>
         </is>
       </c>
-      <c r="O3" s="29" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Enter the Farmer ID.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="29" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B4" s="29" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>fayda_id_entered</t>
         </is>
       </c>
-      <c r="C4" s="29" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Fayda ID</t>
         </is>
       </c>
-      <c r="D4" s="29" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>The 16 digit FAN or the 12 digit FIN. Spaces are allowed.</t>
         </is>
       </c>
-      <c r="E4" s="29" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="F4" s="29" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>regex(translate(., ' ', ''), '^([0-9]{12}|[0-9]{16})$')</t>
         </is>
       </c>
-      <c r="G4" s="29" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>The Fayda ID must be a 16 digit FAN or a 12 digit FIN. Spaces are allowed.</t>
         </is>
       </c>
-      <c r="O4" s="29" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Enter the Fayda ID.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="29" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B5" s="29" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>fayda_id</t>
         </is>
       </c>
-      <c r="I5" s="29" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>translate(${fayda_id_entered}, ' ', '')</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="29" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>end_group</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="29" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>begin_group</t>
         </is>
       </c>
-      <c r="B7" s="29" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>production_season_info</t>
         </is>
       </c>
-      <c r="C7" s="29" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Production Season</t>
         </is>
       </c>
-      <c r="K7" s="29" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>field-list</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="29" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="B8" s="29" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>crop_year</t>
         </is>
       </c>
-      <c r="C8" s="29" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Crop Year</t>
         </is>
       </c>
-      <c r="E8" s="29" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="F8" s="29" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>. = number(format-date(today(), '%Y'))</t>
         </is>
       </c>
-      <c r="G8" s="29" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Only the current crop year is allowed.</t>
         </is>
       </c>
-      <c r="O8" s="29" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Enter the crop year.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="29" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>select_one crop_season</t>
         </is>
       </c>
-      <c r="B9" s="29" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>production_season</t>
         </is>
       </c>
-      <c r="C9" s="29" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Production Season</t>
         </is>
       </c>
-      <c r="E9" s="29" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="O9" s="29" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Select the production season.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="29" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>end_group</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="29" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>begin_repeat</t>
         </is>
       </c>
-      <c r="B11" s="29" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>sowing_details</t>
         </is>
       </c>
-      <c r="C11" s="29" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Sowing Details</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="29" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B12" s="29" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>land_info_id</t>
         </is>
       </c>
-      <c r="C12" s="29" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Land ID</t>
         </is>
       </c>
-      <c r="E12" s="29" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="O12" s="29" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Enter the Land ID.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="29" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>select_multiple cluster_status</t>
         </is>
       </c>
-      <c r="B13" s="29" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>cluster_status_ids</t>
         </is>
       </c>
-      <c r="C13" s="29" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Cluster Status</t>
         </is>
       </c>
-      <c r="K13" s="29" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="29" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>begin_group</t>
         </is>
       </c>
-      <c r="B14" s="29" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>clustered_details</t>
         </is>
       </c>
-      <c r="C14" s="29" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Clustered Details</t>
         </is>
       </c>
-      <c r="H14" s="29" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>selected(${cluster_status_ids}, 'clustered')</t>
         </is>
       </c>
-      <c r="K14" s="29" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>field-list</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="29" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B15" s="29" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>cluster_name</t>
         </is>
       </c>
-      <c r="C15" s="29" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Farmer Production Cluster (FPC) Name</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="29" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>select_one crop_season</t>
         </is>
       </c>
-      <c r="B16" s="29" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>cluster_season_id</t>
         </is>
       </c>
-      <c r="C16" s="29" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Season</t>
         </is>
       </c>
-      <c r="F16" s="29" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>. = ${production_season}</t>
         </is>
       </c>
-      <c r="G16" s="29" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>Season must match the Production Season selected earlier.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="29" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>select_one agro_ecological_zone</t>
         </is>
       </c>
-      <c r="B17" s="29" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>cluster_agro_ecological_zone</t>
         </is>
       </c>
-      <c r="C17" s="29" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Agro Ecological Zone</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="29" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>decimal</t>
         </is>
       </c>
-      <c r="B18" s="29" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>cluster_area_hectare</t>
         </is>
       </c>
-      <c r="C18" s="29" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Total Cultivated Area (ha)</t>
         </is>
       </c>
-      <c r="F18" s="29" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>. &gt;= 0</t>
         </is>
       </c>
-      <c r="G18" s="29" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>Total Cultivated Area cannot be negative.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="29" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>select_one sowing_status</t>
         </is>
       </c>
-      <c r="B19" s="29" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>sowing_status</t>
         </is>
       </c>
-      <c r="C19" s="29" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Sowing Status</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="29" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>decimal</t>
         </is>
       </c>
-      <c r="B20" s="29" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>cluster_area_sown</t>
         </is>
       </c>
-      <c r="C20" s="29" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Area Sown (ha)</t>
         </is>
       </c>
-      <c r="F20" s="29" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>. &gt;= 0</t>
         </is>
       </c>
-      <c r="G20" s="29" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>Area Sown cannot be negative.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="29" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>select_multiple yes_only</t>
         </is>
       </c>
-      <c r="B21" s="29" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>cluster_has_pest_disease</t>
         </is>
       </c>
-      <c r="C21" s="29" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Pest / Disease Occurrence</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="29" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>end_group</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="29" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>begin_group</t>
         </is>
       </c>
-      <c r="B23" s="29" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>independant_details</t>
         </is>
       </c>
-      <c r="C23" s="29" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Independent Details</t>
         </is>
       </c>
-      <c r="H23" s="29" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>selected(${cluster_status_ids}, 'independent')</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="29" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>select_one crop_season</t>
         </is>
       </c>
-      <c r="B24" s="29" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>season_id</t>
         </is>
       </c>
-      <c r="C24" s="29" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>Season</t>
         </is>
       </c>
-      <c r="F24" s="29" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>. = ${production_season}</t>
         </is>
       </c>
-      <c r="G24" s="29" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>Season must match the Production Season selected earlier.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="29" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>decimal</t>
         </is>
       </c>
-      <c r="B25" s="29" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>area_sown</t>
         </is>
       </c>
-      <c r="C25" s="29" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Area Sown (ha)</t>
         </is>
       </c>
-      <c r="F25" s="29" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>. &gt;= 0</t>
         </is>
       </c>
-      <c r="G25" s="29" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>Area Sown cannot be negative.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="29" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>select_one_from_file crop_name.csv</t>
         </is>
       </c>
-      <c r="B26" s="29" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>crop_name_id</t>
         </is>
       </c>
-      <c r="C26" s="29" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>Actual Crop Name</t>
         </is>
       </c>
-      <c r="E26" s="29" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="K26" s="29" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
-      <c r="O26" s="29" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>Select the actual crop name.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="29" t="inlineStr">
+      <c r="A27" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B27" s="29" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>sowing_date_gc</t>
         </is>
       </c>
-      <c r="C27" s="29" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>Sowing Date (Gregorian calendar)</t>
         </is>
       </c>
-      <c r="F27" s="29" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>. &lt;= today()</t>
         </is>
       </c>
-      <c r="G27" s="29" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>Sowing Date cannot be in the future.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="29" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>select_one fertilizer_type</t>
         </is>
       </c>
-      <c r="B28" s="29" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>actual_fertilizer_type</t>
         </is>
       </c>
-      <c r="C28" s="29" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>Actual Fertilizer Type</t>
         </is>
       </c>
-      <c r="K28" s="29" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="29" t="inlineStr">
+      <c r="A29" t="inlineStr">
         <is>
           <t>decimal</t>
         </is>
       </c>
-      <c r="B29" s="29" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>actual_fertilizer_qty</t>
         </is>
       </c>
-      <c r="C29" s="29" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>Actual Fertilizer Quantity (kg)</t>
         </is>
       </c>
-      <c r="F29" s="29" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>. &gt;= 0</t>
         </is>
       </c>
-      <c r="G29" s="29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>Actual Fertilizer Quantity cannot be negative.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="29" t="inlineStr">
+      <c r="A30" t="inlineStr">
         <is>
           <t>select_multiple yes_only</t>
         </is>
       </c>
-      <c r="B30" s="29" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>has_pest_disease</t>
         </is>
       </c>
-      <c r="C30" s="29" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>Pest / Disease Occurrence</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="29" t="inlineStr">
+      <c r="A31" t="inlineStr">
         <is>
           <t>end_group</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="29" t="inlineStr">
+      <c r="A32" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B32" s="29" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>surveyor_name</t>
         </is>
       </c>
-      <c r="C32" s="29" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>Development Agent Name</t>
         </is>
       </c>
-      <c r="F32" s="29" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>regex(., '^[a-zA-Z\u1200-\u137F .\-]+$')</t>
         </is>
       </c>
-      <c r="G32" s="29" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>Enter the Development Agent's name using letters (English or Amharic), spaces, dots and hyphens only.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="29" t="inlineStr">
+      <c r="A33" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B33" s="29" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>surveyor_mobile_number</t>
         </is>
       </c>
-      <c r="C33" s="29" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>Development Agent Mobile Number</t>
         </is>
       </c>
-      <c r="D33" s="29" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>For example 0911223344 or +251911223344</t>
         </is>
       </c>
-      <c r="F33" s="29" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>regex(., '^(\+251[79][0-9]{8}|0[79][0-9]{8})$')</t>
         </is>
       </c>
-      <c r="G33" s="29" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>Enter a valid Ethiopian mobile number, for example 0911223344 or +251911223344.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="29" t="inlineStr">
+      <c r="A34" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B34" s="29" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>supervisor_name</t>
         </is>
       </c>
-      <c r="C34" s="29" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>Supervisor Name</t>
         </is>
       </c>
-      <c r="F34" s="29" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>regex(., '^[a-zA-Z\u1200-\u137F .\-]+$')</t>
         </is>
       </c>
-      <c r="G34" s="29" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>Enter the supervisor's name using letters (English or Amharic), spaces, dots and hyphens only.</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="29" t="inlineStr">
+      <c r="A35" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B35" s="29" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>supervisor_mobile_number</t>
         </is>
       </c>
-      <c r="C35" s="29" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>Supervisor Mobile Number</t>
         </is>
       </c>
-      <c r="D35" s="29" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>For example 0911223344 or +251911223344</t>
         </is>
       </c>
-      <c r="F35" s="29" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>regex(., '^(\+251[79][0-9]{8}|0[79][0-9]{8})$')</t>
         </is>
       </c>
-      <c r="G35" s="29" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>Enter a valid Ethiopian mobile number, for example 0911223344 or +251911223344.</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="29" t="inlineStr">
+      <c r="A36" t="inlineStr">
         <is>
           <t>end_repeat</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="29" t="inlineStr">
+      <c r="A37" t="inlineStr">
         <is>
           <t>begin_repeat</t>
         </is>
       </c>
-      <c r="B37" s="29" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>infestation_incidents</t>
         </is>
       </c>
-      <c r="C37" s="29" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>Infestation Incidents</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="29" t="inlineStr">
+      <c r="A38" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B38" s="29" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>infestation_land_info_id</t>
         </is>
       </c>
-      <c r="C38" s="29" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>Land ID</t>
         </is>
       </c>
-      <c r="E38" s="29" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="F38" s="29" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>selected(join(' ', ${land_info_id}), .)</t>
         </is>
       </c>
-      <c r="G38" s="29" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>Land ID does not match the Land ID provided in Sowing Details. Please enter the correct Land ID.</t>
         </is>
       </c>
-      <c r="O38" s="29" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t>Enter the Land ID.</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="29" t="inlineStr">
+      <c r="A39" t="inlineStr">
         <is>
           <t>select_one cluster_status</t>
         </is>
       </c>
-      <c r="B39" s="29" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>cluster_status_id</t>
         </is>
       </c>
-      <c r="C39" s="29" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>Cluster Status</t>
         </is>
       </c>
-      <c r="K39" s="29" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="29" t="inlineStr">
+      <c r="A40" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B40" s="29" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>infestation_fpc_name</t>
         </is>
       </c>
-      <c r="C40" s="29" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>Farmer Production Cluster (FPC) Name</t>
         </is>
       </c>
-      <c r="H40" s="29" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>selected(${cluster_status_id}, 'clustered')</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="29" t="inlineStr">
+      <c r="A41" t="inlineStr">
         <is>
           <t>select_one_from_file crop_name.csv</t>
         </is>
       </c>
-      <c r="B41" s="29" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>crop_name_id</t>
         </is>
       </c>
-      <c r="C41" s="29" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>Crop Type Affected</t>
         </is>
       </c>
-      <c r="E41" s="29" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H41" s="29" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t xml:space="preserve">selected(${cluster_status_id}, 'independent')
 </t>
         </is>
       </c>
-      <c r="K41" s="29" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
-      <c r="O41" s="29" t="inlineStr">
+      <c r="O41" t="inlineStr">
         <is>
           <t>Select the crop type affected.</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="29" t="inlineStr">
+      <c r="A42" t="inlineStr">
         <is>
           <t>select_multiple infestation_type</t>
         </is>
       </c>
-      <c r="B42" s="29" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>infestation_type_ids</t>
         </is>
       </c>
-      <c r="C42" s="29" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>Type of Infestation</t>
         </is>
       </c>
-      <c r="K42" s="29" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="29" t="inlineStr">
+      <c r="A43" t="inlineStr">
         <is>
           <t>select_one growth_stage</t>
         </is>
       </c>
-      <c r="B43" s="29" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>growth_stage</t>
         </is>
       </c>
-      <c r="C43" s="29" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>Growth Stage</t>
         </is>
       </c>
-      <c r="K43" s="29" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="29" t="inlineStr">
+      <c r="A44" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B44" s="29" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>observation_date</t>
         </is>
       </c>
-      <c r="C44" s="29" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>Date of Observation (Gregorian calendar)</t>
         </is>
       </c>
-      <c r="F44" s="29" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>. &lt;= today()</t>
         </is>
       </c>
-      <c r="G44" s="29" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>Date of Observation cannot be in the future.</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="29" t="inlineStr">
+      <c r="A45" t="inlineStr">
         <is>
           <t>note</t>
         </is>
       </c>
-      <c r="B45" s="29" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>ec_date_message</t>
         </is>
       </c>
-      <c r="C45" s="29" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>The date you select is converted to the Ethiopian calendar automatically.</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="29" t="inlineStr">
+      <c r="A46" t="inlineStr">
         <is>
           <t>select_one security_level</t>
         </is>
       </c>
-      <c r="B46" s="29" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>security_level</t>
         </is>
       </c>
-      <c r="C46" s="29" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>Security Level</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="29" t="inlineStr">
+      <c r="A47" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B47" s="29" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>estimated_damage</t>
         </is>
       </c>
-      <c r="C47" s="29" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>Estimated Crop Damage (percent or hectares)</t>
         </is>
       </c>
-      <c r="D47" s="29" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>Write the amount followed by % or ha, for example 20% or 0.5 ha.</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="29" t="inlineStr">
+      <c r="A48" t="inlineStr">
         <is>
           <t>begin_group</t>
         </is>
       </c>
-      <c r="B48" s="29" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>pest_occurance</t>
         </is>
       </c>
-      <c r="C48" s="29" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>Pest Occurrence</t>
         </is>
       </c>
-      <c r="H48" s="29" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>selected(${infestation_type_ids}, 'pest')</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="29" t="inlineStr">
+      <c r="A49" t="inlineStr">
         <is>
           <t>select_one pest_type</t>
         </is>
       </c>
-      <c r="B49" s="29" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>pest_type</t>
         </is>
       </c>
-      <c r="C49" s="29" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>Pest Type</t>
         </is>
       </c>
-      <c r="K49" s="29" t="inlineStr">
+      <c r="K49" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="29" t="inlineStr">
+      <c r="A50" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B50" s="29" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>pest_name</t>
         </is>
       </c>
-      <c r="C50" s="29" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>Pest Name</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="29" t="inlineStr">
+      <c r="A51" t="inlineStr">
         <is>
           <t>select_one method_control</t>
         </is>
       </c>
-      <c r="B51" s="29" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>pest_pesticide_method</t>
         </is>
       </c>
-      <c r="C51" s="29" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>Method of Control (Pest)</t>
         </is>
       </c>
-      <c r="K51" s="29" t="inlineStr">
+      <c r="K51" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="29" t="inlineStr">
+      <c r="A52" t="inlineStr">
         <is>
           <t>select_one pesticides_type</t>
         </is>
       </c>
-      <c r="B52" s="29" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>pesticide_type</t>
         </is>
       </c>
-      <c r="C52" s="29" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>Pesticide Type</t>
         </is>
       </c>
-      <c r="K52" s="29" t="inlineStr">
+      <c r="K52" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="29" t="inlineStr">
+      <c r="A53" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B53" s="29" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>pesticide_name</t>
         </is>
       </c>
-      <c r="C53" s="29" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>Pesticide Name</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="29" t="inlineStr">
+      <c r="A54" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B54" s="29" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>pest_frequency_of_application</t>
         </is>
       </c>
-      <c r="C54" s="29" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>Frequency of Application</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="29" t="inlineStr">
+      <c r="A55" t="inlineStr">
         <is>
           <t>end_group</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="29" t="inlineStr">
+      <c r="A56" t="inlineStr">
         <is>
           <t>begin_group</t>
         </is>
       </c>
-      <c r="B56" s="29" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>weed_occurrence</t>
         </is>
       </c>
-      <c r="C56" s="29" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>Weed Occurrence</t>
         </is>
       </c>
-      <c r="H56" s="29" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>selected(${infestation_type_ids}, 'weed')</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="29" t="inlineStr">
+      <c r="A57" t="inlineStr">
         <is>
           <t>select_one weed_type</t>
         </is>
       </c>
-      <c r="B57" s="29" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>weed_type</t>
         </is>
       </c>
-      <c r="C57" s="29" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>Weed Type</t>
         </is>
       </c>
-      <c r="K57" s="29" t="inlineStr">
+      <c r="K57" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="29" t="inlineStr">
+      <c r="A58" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B58" s="29" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>weed_name_id</t>
         </is>
       </c>
-      <c r="C58" s="29" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>Weed Name</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="29" t="inlineStr">
+      <c r="A59" t="inlineStr">
         <is>
           <t>select_one method_control</t>
         </is>
       </c>
-      <c r="B59" s="29" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>weed_control_method</t>
         </is>
       </c>
-      <c r="C59" s="29" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>Method of Control (Weed)</t>
         </is>
       </c>
-      <c r="K59" s="29" t="inlineStr">
+      <c r="K59" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="29" t="inlineStr">
+      <c r="A60" t="inlineStr">
         <is>
           <t>select_one weedicides_type</t>
         </is>
       </c>
-      <c r="B60" s="29" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>weedicide_type</t>
         </is>
       </c>
-      <c r="C60" s="29" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>Weedicide Type</t>
         </is>
       </c>
-      <c r="K60" s="29" t="inlineStr">
+      <c r="K60" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="29" t="inlineStr">
+      <c r="A61" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B61" s="29" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>weedicide_name</t>
         </is>
       </c>
-      <c r="C61" s="29" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>Weedicide Name</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="29" t="inlineStr">
+      <c r="A62" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B62" s="29" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>weed_frequency_of_application</t>
         </is>
       </c>
-      <c r="C62" s="29" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>Frequency of Application</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="29" t="inlineStr">
+      <c r="A63" t="inlineStr">
         <is>
           <t>end_group</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="29" t="inlineStr">
+      <c r="A64" t="inlineStr">
         <is>
           <t>begin_group</t>
         </is>
       </c>
-      <c r="B64" s="29" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>disease</t>
         </is>
       </c>
-      <c r="C64" s="29" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>Disease</t>
         </is>
       </c>
-      <c r="H64" s="29" t="inlineStr">
+      <c r="H64" t="inlineStr">
         <is>
           <t>selected(${infestation_type_ids}, 'disease')</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="29" t="inlineStr">
+      <c r="A65" t="inlineStr">
         <is>
           <t>select_one disease_type</t>
         </is>
       </c>
-      <c r="B65" s="29" t="inlineStr">
+      <c r="B65" t="inlineStr">
         <is>
           <t>disease_type</t>
         </is>
       </c>
-      <c r="C65" s="29" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t>Disease Type</t>
         </is>
       </c>
-      <c r="K65" s="29" t="inlineStr">
+      <c r="K65" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="29" t="inlineStr">
+      <c r="A66" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B66" s="29" t="inlineStr">
+      <c r="B66" t="inlineStr">
         <is>
           <t>disease_name</t>
         </is>
       </c>
-      <c r="C66" s="29" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>Disease Name</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="29" t="inlineStr">
+      <c r="A67" t="inlineStr">
         <is>
           <t>select_one method_control</t>
         </is>
       </c>
-      <c r="B67" s="29" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>ind_method_of_control</t>
         </is>
       </c>
-      <c r="C67" s="29" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>Method of Control (Disease)</t>
         </is>
       </c>
-      <c r="K67" s="29" t="inlineStr">
+      <c r="K67" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="29" t="inlineStr">
+      <c r="A68" t="inlineStr">
         <is>
           <t>select_one fungicide_type</t>
         </is>
       </c>
-      <c r="B68" s="29" t="inlineStr">
+      <c r="B68" t="inlineStr">
         <is>
           <t>fungicide_type</t>
         </is>
       </c>
-      <c r="C68" s="29" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>Fungicide / Bactericide Type</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="29" t="inlineStr">
+      <c r="A69" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B69" s="29" t="inlineStr">
+      <c r="B69" t="inlineStr">
         <is>
           <t>fungicide_name</t>
         </is>
       </c>
-      <c r="C69" s="29" t="inlineStr">
+      <c r="C69" t="inlineStr">
         <is>
           <t>Fungicide / Bactericide Name</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="29" t="inlineStr">
+      <c r="A70" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B70" s="29" t="inlineStr">
+      <c r="B70" t="inlineStr">
         <is>
           <t>disease_frequency_of_application</t>
         </is>
       </c>
-      <c r="C70" s="29" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>Frequency of Application</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="29" t="inlineStr">
+      <c r="A71" t="inlineStr">
         <is>
           <t>end_group</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="29" t="inlineStr">
+      <c r="A72" t="inlineStr">
         <is>
           <t>begin_group</t>
         </is>
       </c>
-      <c r="B72" s="29" t="inlineStr">
+      <c r="B72" t="inlineStr">
         <is>
           <t>nutrient_deficiency</t>
         </is>
       </c>
-      <c r="C72" s="29" t="inlineStr">
+      <c r="C72" t="inlineStr">
         <is>
           <t>Nutrient Deficiency</t>
         </is>
       </c>
-      <c r="H72" s="29" t="inlineStr">
+      <c r="H72" t="inlineStr">
         <is>
           <t>selected(${infestation_type_ids}, 'nutrient_deficiency')</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="29" t="inlineStr">
+      <c r="A73" t="inlineStr">
         <is>
           <t>select_one nutrient_type</t>
         </is>
       </c>
-      <c r="B73" s="29" t="inlineStr">
+      <c r="B73" t="inlineStr">
         <is>
           <t>nutrient_type</t>
         </is>
       </c>
-      <c r="C73" s="29" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>Nutrient Type</t>
         </is>
       </c>
-      <c r="K73" s="29" t="inlineStr">
+      <c r="K73" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="29" t="inlineStr">
+      <c r="A74" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B74" s="29" t="inlineStr">
+      <c r="B74" t="inlineStr">
         <is>
           <t>nutrient_name</t>
         </is>
       </c>
-      <c r="C74" s="29" t="inlineStr">
+      <c r="C74" t="inlineStr">
         <is>
           <t>Nutrient Name</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="29" t="inlineStr">
+      <c r="A75" t="inlineStr">
         <is>
           <t>select_one method_of_control</t>
         </is>
       </c>
-      <c r="B75" s="29" t="inlineStr">
+      <c r="B75" t="inlineStr">
         <is>
           <t>method_of_control</t>
         </is>
       </c>
-      <c r="C75" s="29" t="inlineStr">
+      <c r="C75" t="inlineStr">
         <is>
           <t>Method of Control (Nutrient)</t>
         </is>
       </c>
-      <c r="K75" s="29" t="inlineStr">
+      <c r="K75" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="29" t="inlineStr">
+      <c r="A76" t="inlineStr">
         <is>
           <t>select_one fert_type</t>
         </is>
       </c>
-      <c r="B76" s="29" t="inlineStr">
+      <c r="B76" t="inlineStr">
         <is>
           <t>fertilizer_type</t>
         </is>
       </c>
-      <c r="C76" s="29" t="inlineStr">
+      <c r="C76" t="inlineStr">
         <is>
           <t>Fertilizer / Amendment Type</t>
         </is>
       </c>
-      <c r="K76" s="29" t="inlineStr">
+      <c r="K76" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="29" t="inlineStr">
+      <c r="A77" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B77" s="29" t="inlineStr">
+      <c r="B77" t="inlineStr">
         <is>
           <t>fertilizer_name</t>
         </is>
       </c>
-      <c r="C77" s="29" t="inlineStr">
+      <c r="C77" t="inlineStr">
         <is>
           <t>Fertilizer / Amendment Name</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="29" t="inlineStr">
+      <c r="A78" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B78" s="29" t="inlineStr">
+      <c r="B78" t="inlineStr">
         <is>
           <t>nutrient_frequency_of_application</t>
         </is>
       </c>
-      <c r="C78" s="29" t="inlineStr">
+      <c r="C78" t="inlineStr">
         <is>
           <t>Frequency of Application</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="29" t="inlineStr">
+      <c r="A79" t="inlineStr">
         <is>
           <t>end_group</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="29" t="inlineStr">
+      <c r="A80" t="inlineStr">
         <is>
           <t>begin_group</t>
         </is>
       </c>
-      <c r="B80" s="29" t="inlineStr">
+      <c r="B80" t="inlineStr">
         <is>
           <t>climate_shock</t>
         </is>
       </c>
-      <c r="C80" s="29" t="inlineStr">
+      <c r="C80" t="inlineStr">
         <is>
           <t>Climate Shock</t>
         </is>
       </c>
-      <c r="H80" s="29" t="inlineStr">
+      <c r="H80" t="inlineStr">
         <is>
           <t>selected(${infestation_type_ids}, 'climate_shock')</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="29" t="inlineStr">
+      <c r="A81" t="inlineStr">
         <is>
           <t>select_one shock_type</t>
         </is>
       </c>
-      <c r="B81" s="29" t="inlineStr">
+      <c r="B81" t="inlineStr">
         <is>
           <t>shock_type</t>
         </is>
       </c>
-      <c r="C81" s="29" t="inlineStr">
+      <c r="C81" t="inlineStr">
         <is>
           <t>Shock Type</t>
         </is>
       </c>
-      <c r="K81" s="29" t="inlineStr">
+      <c r="K81" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="29" t="inlineStr">
+      <c r="A82" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B82" s="29" t="inlineStr">
+      <c r="B82" t="inlineStr">
         <is>
           <t>shock_event_name</t>
         </is>
       </c>
-      <c r="C82" s="29" t="inlineStr">
+      <c r="C82" t="inlineStr">
         <is>
           <t>Shock Event Name / Description</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="29" t="inlineStr">
+      <c r="A83" t="inlineStr">
         <is>
           <t>select_one m_control</t>
         </is>
       </c>
-      <c r="B83" s="29" t="inlineStr">
+      <c r="B83" t="inlineStr">
         <is>
           <t>climate_method_of_control</t>
         </is>
       </c>
-      <c r="C83" s="29" t="inlineStr">
+      <c r="C83" t="inlineStr">
         <is>
           <t>Method of Control (Climate)</t>
         </is>
       </c>
-      <c r="K83" s="29" t="inlineStr">
+      <c r="K83" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="29" t="inlineStr">
+      <c r="A84" t="inlineStr">
         <is>
           <t>select_one recovery_type</t>
         </is>
       </c>
-      <c r="B84" s="29" t="inlineStr">
+      <c r="B84" t="inlineStr">
         <is>
           <t>recovery_input_type</t>
         </is>
       </c>
-      <c r="C84" s="29" t="inlineStr">
+      <c r="C84" t="inlineStr">
         <is>
           <t>Recovery Input Type</t>
         </is>
       </c>
-      <c r="K84" s="29" t="inlineStr">
+      <c r="K84" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="29" t="inlineStr">
+      <c r="A85" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B85" s="29" t="inlineStr">
+      <c r="B85" t="inlineStr">
         <is>
           <t>recovery_input_name</t>
         </is>
       </c>
-      <c r="C85" s="29" t="inlineStr">
+      <c r="C85" t="inlineStr">
         <is>
           <t>Recovery Input Name</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="29" t="inlineStr">
+      <c r="A86" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B86" s="29" t="inlineStr">
+      <c r="B86" t="inlineStr">
         <is>
           <t>recovery_frequency_of_application</t>
         </is>
       </c>
-      <c r="C86" s="29" t="inlineStr">
+      <c r="C86" t="inlineStr">
         <is>
           <t>Frequency of Application</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="29" t="inlineStr">
+      <c r="A87" t="inlineStr">
         <is>
           <t>end_group</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="29" t="inlineStr">
+      <c r="A88" t="inlineStr">
         <is>
           <t>end_repeat</t>
         </is>
@@ -2416,2383 +2416,2383 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="29" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>list_name</t>
         </is>
       </c>
-      <c r="B1" s="29" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C1" s="29" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>label</t>
         </is>
       </c>
-      <c r="D1" s="29" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="E1" s="29" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>fert_type</t>
         </is>
       </c>
-      <c r="F1" s="29" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pest_name</t>
         </is>
       </c>
-      <c r="G1" s="29" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>weed_name</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="29" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>infestation_type</t>
         </is>
       </c>
-      <c r="B2" s="29" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>pest</t>
         </is>
       </c>
-      <c r="C2" s="29" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Pest (ተባይ)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="29" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>infestation_type</t>
         </is>
       </c>
-      <c r="B3" s="29" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>weed</t>
         </is>
       </c>
-      <c r="C3" s="29" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Weed</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="29" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>infestation_type</t>
         </is>
       </c>
-      <c r="B4" s="29" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>disease</t>
         </is>
       </c>
-      <c r="C4" s="29" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Disease (በሽታ)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="29" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>infestation_type</t>
         </is>
       </c>
-      <c r="B5" s="29" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>nutrient_deficiency</t>
         </is>
       </c>
-      <c r="C5" s="29" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Nutrient Deficiency (የንጥረ ነገር እጥረት)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="29" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>infestation_type</t>
         </is>
       </c>
-      <c r="B6" s="29" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>climate_shock</t>
         </is>
       </c>
-      <c r="C6" s="29" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Climate Shock</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="29" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>growth_stage</t>
         </is>
       </c>
-      <c r="B7" s="29" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>emergence</t>
         </is>
       </c>
-      <c r="C7" s="29" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Emergence</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="29" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>growth_stage</t>
         </is>
       </c>
-      <c r="B8" s="29" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>vegetative</t>
         </is>
       </c>
-      <c r="C8" s="29" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Vegetative</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="29" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>growth_stage</t>
         </is>
       </c>
-      <c r="B9" s="29" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>flowering</t>
         </is>
       </c>
-      <c r="C9" s="29" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Flowering</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="29" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>growth_stage</t>
         </is>
       </c>
-      <c r="B10" s="29" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>maturity</t>
         </is>
       </c>
-      <c r="C10" s="29" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Maturity</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="29" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>security_level</t>
         </is>
       </c>
-      <c r="B11" s="29" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="C11" s="29" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Low (ቀላል)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="29" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>security_level</t>
         </is>
       </c>
-      <c r="B12" s="29" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="C12" s="29" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Medium (መካከለኛ)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="29" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>security_level</t>
         </is>
       </c>
-      <c r="B13" s="29" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="C13" s="29" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>High (ከፍተኛ)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="29" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>method_control</t>
         </is>
       </c>
-      <c r="B14" s="29" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>chemical_spray</t>
         </is>
       </c>
-      <c r="C14" s="29" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Chemical Spray</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="29" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>method_control</t>
         </is>
       </c>
-      <c r="B15" s="29" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>hand_picking</t>
         </is>
       </c>
-      <c r="C15" s="29" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Hand Picking</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="29" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>method_control</t>
         </is>
       </c>
-      <c r="B16" s="29" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>early_harvesting</t>
         </is>
       </c>
-      <c r="C16" s="29" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Early Harvesting</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="29" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>nutrient_type</t>
         </is>
       </c>
-      <c r="B17" s="29" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>macronutrient</t>
         </is>
       </c>
-      <c r="C17" s="29" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Macronutrient</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="29" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>nutrient_type</t>
         </is>
       </c>
-      <c r="B18" s="29" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>secondary_nutrient</t>
         </is>
       </c>
-      <c r="C18" s="29" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Secondary Nutrient</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="29" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>nutrient_type</t>
         </is>
       </c>
-      <c r="B19" s="29" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>micronutrient</t>
         </is>
       </c>
-      <c r="C19" s="29" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Micronutrient</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="29" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>method_of_control</t>
         </is>
       </c>
-      <c r="B20" s="29" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>soil_application</t>
         </is>
       </c>
-      <c r="C20" s="29" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Soil Application</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="29" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>method_of_control</t>
         </is>
       </c>
-      <c r="B21" s="29" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>foliar_spray</t>
         </is>
       </c>
-      <c r="C21" s="29" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Foliar Spray</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="29" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>method_of_control</t>
         </is>
       </c>
-      <c r="B22" s="29" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>organic_amendment</t>
         </is>
       </c>
-      <c r="C22" s="29" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Organic Amendment</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="29" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>method_of_control</t>
         </is>
       </c>
-      <c r="B23" s="29" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>cultural</t>
         </is>
       </c>
-      <c r="C23" s="29" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Cultural (for example liming or crop rotation)</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="29" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>fert_type</t>
         </is>
       </c>
-      <c r="B24" s="29" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>organic</t>
         </is>
       </c>
-      <c r="C24" s="29" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>Organic</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="29" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>fert_type</t>
         </is>
       </c>
-      <c r="B25" s="29" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>inorganic</t>
         </is>
       </c>
-      <c r="C25" s="29" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Inorganic</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="29" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>shock_type</t>
         </is>
       </c>
-      <c r="B26" s="29" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>frost</t>
         </is>
       </c>
-      <c r="C26" s="29" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>Frost</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="29" t="inlineStr">
+      <c r="A27" t="inlineStr">
         <is>
           <t>shock_type</t>
         </is>
       </c>
-      <c r="B27" s="29" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>flood</t>
         </is>
       </c>
-      <c r="C27" s="29" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>Flood</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="29" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>shock_type</t>
         </is>
       </c>
-      <c r="B28" s="29" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>hail</t>
         </is>
       </c>
-      <c r="C28" s="29" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>Hail</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="29" t="inlineStr">
+      <c r="A29" t="inlineStr">
         <is>
           <t>shock_type</t>
         </is>
       </c>
-      <c r="B29" s="29" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>drought</t>
         </is>
       </c>
-      <c r="C29" s="29" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>Drought</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="29" t="inlineStr">
+      <c r="A30" t="inlineStr">
         <is>
           <t>m_control</t>
         </is>
       </c>
-      <c r="B30" s="29" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>drainage</t>
         </is>
       </c>
-      <c r="C30" s="29" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>Drainage</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="29" t="inlineStr">
+      <c r="A31" t="inlineStr">
         <is>
           <t>m_control</t>
         </is>
       </c>
-      <c r="B31" s="29" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>irrigation</t>
         </is>
       </c>
-      <c r="C31" s="29" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>Irrigation</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="29" t="inlineStr">
+      <c r="A32" t="inlineStr">
         <is>
           <t>m_control</t>
         </is>
       </c>
-      <c r="B32" s="29" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>shelter_covering</t>
         </is>
       </c>
-      <c r="C32" s="29" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>Shelter / Covering</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="29" t="inlineStr">
+      <c r="A33" t="inlineStr">
         <is>
           <t>m_control</t>
         </is>
       </c>
-      <c r="B33" s="29" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>replanting</t>
         </is>
       </c>
-      <c r="C33" s="29" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>Replanting</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="29" t="inlineStr">
+      <c r="A34" t="inlineStr">
         <is>
           <t>m_control</t>
         </is>
       </c>
-      <c r="B34" s="29" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>windbreak</t>
         </is>
       </c>
-      <c r="C34" s="29" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>Windbreak</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="29" t="inlineStr">
+      <c r="A35" t="inlineStr">
         <is>
           <t>m_control</t>
         </is>
       </c>
-      <c r="B35" s="29" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="C35" s="29" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="29" t="inlineStr">
+      <c r="A36" t="inlineStr">
         <is>
           <t>recovery_type</t>
         </is>
       </c>
-      <c r="B36" s="29" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>soil_conditioner</t>
         </is>
       </c>
-      <c r="C36" s="29" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>Soil Conditioner</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="29" t="inlineStr">
+      <c r="A37" t="inlineStr">
         <is>
           <t>recovery_type</t>
         </is>
       </c>
-      <c r="B37" s="29" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>replanting_material</t>
         </is>
       </c>
-      <c r="C37" s="29" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>Replanting Material</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="29" t="inlineStr">
+      <c r="A38" t="inlineStr">
         <is>
           <t>recovery_type</t>
         </is>
       </c>
-      <c r="B38" s="29" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>irrigation_equipment</t>
         </is>
       </c>
-      <c r="C38" s="29" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>Irrigation Equipment</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="29" t="inlineStr">
+      <c r="A39" t="inlineStr">
         <is>
           <t>recovery_type</t>
         </is>
       </c>
-      <c r="B39" s="29" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="C39" s="29" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="29" t="inlineStr">
+      <c r="A40" t="inlineStr">
         <is>
           <t>yes_only</t>
         </is>
       </c>
-      <c r="B40" s="29" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="C40" s="29" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="29" t="inlineStr">
+      <c r="A41" t="inlineStr">
         <is>
           <t>fertilizer_type</t>
         </is>
       </c>
-      <c r="B41" s="29" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>organic</t>
         </is>
       </c>
-      <c r="C41" s="29" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>Organic</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="29" t="inlineStr">
+      <c r="A42" t="inlineStr">
         <is>
           <t>fertilizer_type</t>
         </is>
       </c>
-      <c r="B42" s="29" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>inorganic</t>
         </is>
       </c>
-      <c r="C42" s="29" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>Inorganic</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="29" t="inlineStr">
+      <c r="A43" t="inlineStr">
         <is>
           <t>fertilizer_type</t>
         </is>
       </c>
-      <c r="B43" s="29" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>bio_fertilizer</t>
         </is>
       </c>
-      <c r="C43" s="29" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>Bio-fertilizer</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="29" t="inlineStr">
+      <c r="A44" t="inlineStr">
         <is>
           <t>pest_type</t>
         </is>
       </c>
-      <c r="B44" s="29" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>aphids</t>
         </is>
       </c>
-      <c r="C44" s="29" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>Aphids</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="29" t="inlineStr">
+      <c r="A45" t="inlineStr">
         <is>
           <t>pest_type</t>
         </is>
       </c>
-      <c r="B45" s="29" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>whiteflies</t>
         </is>
       </c>
-      <c r="C45" s="29" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>Whiteflies</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="29" t="inlineStr">
+      <c r="A46" t="inlineStr">
         <is>
           <t>pest_type</t>
         </is>
       </c>
-      <c r="B46" s="29" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>thrips</t>
         </is>
       </c>
-      <c r="C46" s="29" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>Thrips</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="29" t="inlineStr">
+      <c r="A47" t="inlineStr">
         <is>
           <t>pest_type</t>
         </is>
       </c>
-      <c r="B47" s="29" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>stem_borer</t>
         </is>
       </c>
-      <c r="C47" s="29" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>Stem borer</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="29" t="inlineStr">
+      <c r="A48" t="inlineStr">
         <is>
           <t>pest_type</t>
         </is>
       </c>
-      <c r="B48" s="29" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>leaf_miner</t>
         </is>
       </c>
-      <c r="C48" s="29" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>Leaf miner</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="29" t="inlineStr">
+      <c r="A49" t="inlineStr">
         <is>
           <t>pest_type</t>
         </is>
       </c>
-      <c r="B49" s="29" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>armyworm</t>
         </is>
       </c>
-      <c r="C49" s="29" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>Armyworm</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="29" t="inlineStr">
+      <c r="A50" t="inlineStr">
         <is>
           <t>pest_type</t>
         </is>
       </c>
-      <c r="B50" s="29" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>cutworm</t>
         </is>
       </c>
-      <c r="C50" s="29" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>Cutworm</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="29" t="inlineStr">
+      <c r="A51" t="inlineStr">
         <is>
           <t>pest_type</t>
         </is>
       </c>
-      <c r="B51" s="29" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>bollworm</t>
         </is>
       </c>
-      <c r="C51" s="29" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>Bollworm</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="29" t="inlineStr">
+      <c r="A52" t="inlineStr">
         <is>
           <t>pest_type</t>
         </is>
       </c>
-      <c r="B52" s="29" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>beetles</t>
         </is>
       </c>
-      <c r="C52" s="29" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>Beetles</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="29" t="inlineStr">
+      <c r="A53" t="inlineStr">
         <is>
           <t>pest_type</t>
         </is>
       </c>
-      <c r="B53" s="29" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>mealybugs</t>
         </is>
       </c>
-      <c r="C53" s="29" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>Mealybugs</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="29" t="inlineStr">
+      <c r="A54" t="inlineStr">
         <is>
           <t>pest_type</t>
         </is>
       </c>
-      <c r="B54" s="29" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>grasshoppers</t>
         </is>
       </c>
-      <c r="C54" s="29" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>Grasshoppers</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="29" t="inlineStr">
+      <c r="A55" t="inlineStr">
         <is>
           <t>pest_type</t>
         </is>
       </c>
-      <c r="B55" s="29" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>leafhopper_(jassids)</t>
         </is>
       </c>
-      <c r="C55" s="29" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>Leafhopper (Jassids)</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="29" t="inlineStr">
+      <c r="A56" t="inlineStr">
         <is>
           <t>pest_type</t>
         </is>
       </c>
-      <c r="B56" s="29" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>rats</t>
         </is>
       </c>
-      <c r="C56" s="29" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>Rats</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="29" t="inlineStr">
+      <c r="A57" t="inlineStr">
         <is>
           <t>pest_type</t>
         </is>
       </c>
-      <c r="B57" s="29" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>field_mouse</t>
         </is>
       </c>
-      <c r="C57" s="29" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>Field mouse</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="29" t="inlineStr">
+      <c r="A58" t="inlineStr">
         <is>
           <t>pest_type</t>
         </is>
       </c>
-      <c r="B58" s="29" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>snails</t>
         </is>
       </c>
-      <c r="C58" s="29" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>Snails</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="29" t="inlineStr">
+      <c r="A59" t="inlineStr">
         <is>
           <t>pest_type</t>
         </is>
       </c>
-      <c r="B59" s="29" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>slugs</t>
         </is>
       </c>
-      <c r="C59" s="29" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>Slugs</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="29" t="inlineStr">
+      <c r="A60" t="inlineStr">
         <is>
           <t>pest_type</t>
         </is>
       </c>
-      <c r="B60" s="29" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>leaf_spot</t>
         </is>
       </c>
-      <c r="C60" s="29" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>Leaf spot</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="29" t="inlineStr">
+      <c r="A61" t="inlineStr">
         <is>
           <t>pest_type</t>
         </is>
       </c>
-      <c r="B61" s="29" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>powdery_mildew</t>
         </is>
       </c>
-      <c r="C61" s="29" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>Powdery mildew</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="29" t="inlineStr">
+      <c r="A62" t="inlineStr">
         <is>
           <t>pest_type</t>
         </is>
       </c>
-      <c r="B62" s="29" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>downy_mildew</t>
         </is>
       </c>
-      <c r="C62" s="29" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>Downy mildew</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="29" t="inlineStr">
+      <c r="A63" t="inlineStr">
         <is>
           <t>pest_type</t>
         </is>
       </c>
-      <c r="B63" s="29" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>rust</t>
         </is>
       </c>
-      <c r="C63" s="29" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>Rust</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="29" t="inlineStr">
+      <c r="A64" t="inlineStr">
         <is>
           <t>pest_type</t>
         </is>
       </c>
-      <c r="B64" s="29" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>blight</t>
         </is>
       </c>
-      <c r="C64" s="29" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>Blight</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="29" t="inlineStr">
+      <c r="A65" t="inlineStr">
         <is>
           <t>pest_type</t>
         </is>
       </c>
-      <c r="B65" s="29" t="inlineStr">
+      <c r="B65" t="inlineStr">
         <is>
           <t>wilt</t>
         </is>
       </c>
-      <c r="C65" s="29" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t>Wilt</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="29" t="inlineStr">
+      <c r="A66" t="inlineStr">
         <is>
           <t>pesticides_type</t>
         </is>
       </c>
-      <c r="B66" s="29" t="inlineStr">
+      <c r="B66" t="inlineStr">
         <is>
           <t>insecticide</t>
         </is>
       </c>
-      <c r="C66" s="29" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>Insecticide</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="29" t="inlineStr">
+      <c r="A67" t="inlineStr">
         <is>
           <t>pesticides_type</t>
         </is>
       </c>
-      <c r="B67" s="29" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>fungicide</t>
         </is>
       </c>
-      <c r="C67" s="29" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>Fungicide</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="29" t="inlineStr">
+      <c r="A68" t="inlineStr">
         <is>
           <t>pesticides_type</t>
         </is>
       </c>
-      <c r="B68" s="29" t="inlineStr">
+      <c r="B68" t="inlineStr">
         <is>
           <t>herbicide</t>
         </is>
       </c>
-      <c r="C68" s="29" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>Herbicide</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="29" t="inlineStr">
+      <c r="A69" t="inlineStr">
         <is>
           <t>pesticides_type</t>
         </is>
       </c>
-      <c r="B69" s="29" t="inlineStr">
+      <c r="B69" t="inlineStr">
         <is>
           <t>rodenticide</t>
         </is>
       </c>
-      <c r="C69" s="29" t="inlineStr">
+      <c r="C69" t="inlineStr">
         <is>
           <t>Rodenticide</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="29" t="inlineStr">
+      <c r="A70" t="inlineStr">
         <is>
           <t>pesticides_type</t>
         </is>
       </c>
-      <c r="B70" s="29" t="inlineStr">
+      <c r="B70" t="inlineStr">
         <is>
           <t>bactericide</t>
         </is>
       </c>
-      <c r="C70" s="29" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>Bactericide</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="29" t="inlineStr">
+      <c r="A71" t="inlineStr">
         <is>
           <t>pesticides_type</t>
         </is>
       </c>
-      <c r="B71" s="29" t="inlineStr">
+      <c r="B71" t="inlineStr">
         <is>
           <t>nematicide</t>
         </is>
       </c>
-      <c r="C71" s="29" t="inlineStr">
+      <c r="C71" t="inlineStr">
         <is>
           <t>Nematicide</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="29" t="inlineStr">
+      <c r="A72" t="inlineStr">
         <is>
           <t>pesticides_type</t>
         </is>
       </c>
-      <c r="B72" s="29" t="inlineStr">
+      <c r="B72" t="inlineStr">
         <is>
           <t>acaricide_miticide</t>
         </is>
       </c>
-      <c r="C72" s="29" t="inlineStr">
+      <c r="C72" t="inlineStr">
         <is>
           <t>Acaricide / Miticide</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="29" t="inlineStr">
+      <c r="A73" t="inlineStr">
         <is>
           <t>pesticides_type</t>
         </is>
       </c>
-      <c r="B73" s="29" t="inlineStr">
+      <c r="B73" t="inlineStr">
         <is>
           <t>molluscicide</t>
         </is>
       </c>
-      <c r="C73" s="29" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>Molluscicide</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="29" t="inlineStr">
+      <c r="A74" t="inlineStr">
         <is>
           <t>pesticides_type</t>
         </is>
       </c>
-      <c r="B74" s="29" t="inlineStr">
+      <c r="B74" t="inlineStr">
         <is>
           <t>termiticide</t>
         </is>
       </c>
-      <c r="C74" s="29" t="inlineStr">
+      <c r="C74" t="inlineStr">
         <is>
           <t>Termiticide</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="29" t="inlineStr">
+      <c r="A75" t="inlineStr">
         <is>
           <t>pesticides_type</t>
         </is>
       </c>
-      <c r="B75" s="29" t="inlineStr">
+      <c r="B75" t="inlineStr">
         <is>
           <t>avicide</t>
         </is>
       </c>
-      <c r="C75" s="29" t="inlineStr">
+      <c r="C75" t="inlineStr">
         <is>
           <t>Avicide</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="29" t="inlineStr">
+      <c r="A76" t="inlineStr">
         <is>
           <t>pesticides_type</t>
         </is>
       </c>
-      <c r="B76" s="29" t="inlineStr">
+      <c r="B76" t="inlineStr">
         <is>
           <t>piscicide</t>
         </is>
       </c>
-      <c r="C76" s="29" t="inlineStr">
+      <c r="C76" t="inlineStr">
         <is>
           <t>Piscicide</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="29" t="inlineStr">
+      <c r="A77" t="inlineStr">
         <is>
           <t>pesticides_type</t>
         </is>
       </c>
-      <c r="B77" s="29" t="inlineStr">
+      <c r="B77" t="inlineStr">
         <is>
           <t>algicide</t>
         </is>
       </c>
-      <c r="C77" s="29" t="inlineStr">
+      <c r="C77" t="inlineStr">
         <is>
           <t>Algicide</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="29" t="inlineStr">
+      <c r="A78" t="inlineStr">
         <is>
           <t>pesticides_type</t>
         </is>
       </c>
-      <c r="B78" s="29" t="inlineStr">
+      <c r="B78" t="inlineStr">
         <is>
           <t>virucide</t>
         </is>
       </c>
-      <c r="C78" s="29" t="inlineStr">
+      <c r="C78" t="inlineStr">
         <is>
           <t>Virucide</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="29" t="inlineStr">
+      <c r="A79" t="inlineStr">
         <is>
           <t>weedicides_type</t>
         </is>
       </c>
-      <c r="B79" s="29" t="inlineStr">
+      <c r="B79" t="inlineStr">
         <is>
           <t>pre_emergent_herbicide</t>
         </is>
       </c>
-      <c r="C79" s="29" t="inlineStr">
+      <c r="C79" t="inlineStr">
         <is>
           <t>Pre-emergent Herbicide</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="29" t="inlineStr">
+      <c r="A80" t="inlineStr">
         <is>
           <t>weedicides_type</t>
         </is>
       </c>
-      <c r="B80" s="29" t="inlineStr">
+      <c r="B80" t="inlineStr">
         <is>
           <t>post_emergent_herbicide</t>
         </is>
       </c>
-      <c r="C80" s="29" t="inlineStr">
+      <c r="C80" t="inlineStr">
         <is>
           <t>Post-emergent Herbicide</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="29" t="inlineStr">
+      <c r="A81" t="inlineStr">
         <is>
           <t>weedicides_type</t>
         </is>
       </c>
-      <c r="B81" s="29" t="inlineStr">
+      <c r="B81" t="inlineStr">
         <is>
           <t>systemic_herbicide</t>
         </is>
       </c>
-      <c r="C81" s="29" t="inlineStr">
+      <c r="C81" t="inlineStr">
         <is>
           <t>Systemic Herbicide</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="29" t="inlineStr">
+      <c r="A82" t="inlineStr">
         <is>
           <t>weedicides_type</t>
         </is>
       </c>
-      <c r="B82" s="29" t="inlineStr">
+      <c r="B82" t="inlineStr">
         <is>
           <t>contact_herbicide</t>
         </is>
       </c>
-      <c r="C82" s="29" t="inlineStr">
+      <c r="C82" t="inlineStr">
         <is>
           <t>Contact Herbicide</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="29" t="inlineStr">
+      <c r="A83" t="inlineStr">
         <is>
           <t>weedicides_type</t>
         </is>
       </c>
-      <c r="B83" s="29" t="inlineStr">
+      <c r="B83" t="inlineStr">
         <is>
           <t>graminicide</t>
         </is>
       </c>
-      <c r="C83" s="29" t="inlineStr">
+      <c r="C83" t="inlineStr">
         <is>
           <t>Graminicide</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="29" t="inlineStr">
+      <c r="A84" t="inlineStr">
         <is>
           <t>weedicides_type</t>
         </is>
       </c>
-      <c r="B84" s="29" t="inlineStr">
+      <c r="B84" t="inlineStr">
         <is>
           <t>broadleaf_herbicide</t>
         </is>
       </c>
-      <c r="C84" s="29" t="inlineStr">
+      <c r="C84" t="inlineStr">
         <is>
           <t>Broadleaf Herbicide</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="29" t="inlineStr">
+      <c r="A85" t="inlineStr">
         <is>
           <t>weedicides_type</t>
         </is>
       </c>
-      <c r="B85" s="29" t="inlineStr">
+      <c r="B85" t="inlineStr">
         <is>
           <t>sedge_herbicide</t>
         </is>
       </c>
-      <c r="C85" s="29" t="inlineStr">
+      <c r="C85" t="inlineStr">
         <is>
           <t>Sedge Herbicide</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="29" t="inlineStr">
+      <c r="A86" t="inlineStr">
         <is>
           <t>weedicides_type</t>
         </is>
       </c>
-      <c r="B86" s="29" t="inlineStr">
+      <c r="B86" t="inlineStr">
         <is>
           <t>aquatic_herbicide</t>
         </is>
       </c>
-      <c r="C86" s="29" t="inlineStr">
+      <c r="C86" t="inlineStr">
         <is>
           <t>Aquatic Herbicide</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="29" t="inlineStr">
+      <c r="A87" t="inlineStr">
         <is>
           <t>weedicides_type</t>
         </is>
       </c>
-      <c r="B87" s="29" t="inlineStr">
+      <c r="B87" t="inlineStr">
         <is>
           <t>foliar_herbicide</t>
         </is>
       </c>
-      <c r="C87" s="29" t="inlineStr">
+      <c r="C87" t="inlineStr">
         <is>
           <t>Foliar Herbicide</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="29" t="inlineStr">
+      <c r="A88" t="inlineStr">
         <is>
           <t>weedicides_type</t>
         </is>
       </c>
-      <c r="B88" s="29" t="inlineStr">
+      <c r="B88" t="inlineStr">
         <is>
           <t>soil_herbicide</t>
         </is>
       </c>
-      <c r="C88" s="29" t="inlineStr">
+      <c r="C88" t="inlineStr">
         <is>
           <t>Soil Herbicide</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="29" t="inlineStr">
+      <c r="A89" t="inlineStr">
         <is>
           <t>weed_type</t>
         </is>
       </c>
-      <c r="B89" s="29" t="inlineStr">
+      <c r="B89" t="inlineStr">
         <is>
           <t>annual_weed</t>
         </is>
       </c>
-      <c r="C89" s="29" t="inlineStr">
+      <c r="C89" t="inlineStr">
         <is>
           <t>Annual weed</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="29" t="inlineStr">
+      <c r="A90" t="inlineStr">
         <is>
           <t>weed_type</t>
         </is>
       </c>
-      <c r="B90" s="29" t="inlineStr">
+      <c r="B90" t="inlineStr">
         <is>
           <t>biennial_weed</t>
         </is>
       </c>
-      <c r="C90" s="29" t="inlineStr">
+      <c r="C90" t="inlineStr">
         <is>
           <t>Biennial weed</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="29" t="inlineStr">
+      <c r="A91" t="inlineStr">
         <is>
           <t>weed_type</t>
         </is>
       </c>
-      <c r="B91" s="29" t="inlineStr">
+      <c r="B91" t="inlineStr">
         <is>
           <t>perennial_weed</t>
         </is>
       </c>
-      <c r="C91" s="29" t="inlineStr">
+      <c r="C91" t="inlineStr">
         <is>
           <t>Perennial weed</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="29" t="inlineStr">
+      <c r="A92" t="inlineStr">
         <is>
           <t>weed_type</t>
         </is>
       </c>
-      <c r="B92" s="29" t="inlineStr">
+      <c r="B92" t="inlineStr">
         <is>
           <t>kharif_summer</t>
         </is>
       </c>
-      <c r="C92" s="29" t="inlineStr">
+      <c r="C92" t="inlineStr">
         <is>
           <t>Kharif / Summer</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="29" t="inlineStr">
+      <c r="A93" t="inlineStr">
         <is>
           <t>weed_type</t>
         </is>
       </c>
-      <c r="B93" s="29" t="inlineStr">
+      <c r="B93" t="inlineStr">
         <is>
           <t>rabi_winter</t>
         </is>
       </c>
-      <c r="C93" s="29" t="inlineStr">
+      <c r="C93" t="inlineStr">
         <is>
           <t>Rabi / Winter</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="29" t="inlineStr">
+      <c r="A94" t="inlineStr">
         <is>
           <t>weed_type</t>
         </is>
       </c>
-      <c r="B94" s="29" t="inlineStr">
+      <c r="B94" t="inlineStr">
         <is>
           <t>year_round</t>
         </is>
       </c>
-      <c r="C94" s="29" t="inlineStr">
+      <c r="C94" t="inlineStr">
         <is>
           <t>Year-round</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="29" t="inlineStr">
+      <c r="A95" t="inlineStr">
         <is>
           <t>weed_type</t>
         </is>
       </c>
-      <c r="B95" s="29" t="inlineStr">
+      <c r="B95" t="inlineStr">
         <is>
           <t>grassy</t>
         </is>
       </c>
-      <c r="C95" s="29" t="inlineStr">
+      <c r="C95" t="inlineStr">
         <is>
           <t>Grassy</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="29" t="inlineStr">
+      <c r="A96" t="inlineStr">
         <is>
           <t>weed_type</t>
         </is>
       </c>
-      <c r="B96" s="29" t="inlineStr">
+      <c r="B96" t="inlineStr">
         <is>
           <t>sedge</t>
         </is>
       </c>
-      <c r="C96" s="29" t="inlineStr">
+      <c r="C96" t="inlineStr">
         <is>
           <t>Sedge</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="29" t="inlineStr">
+      <c r="A97" t="inlineStr">
         <is>
           <t>weed_type</t>
         </is>
       </c>
-      <c r="B97" s="29" t="inlineStr">
+      <c r="B97" t="inlineStr">
         <is>
           <t>broadleaf</t>
         </is>
       </c>
-      <c r="C97" s="29" t="inlineStr">
+      <c r="C97" t="inlineStr">
         <is>
           <t>Broadleaf</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="29" t="inlineStr">
+      <c r="A98" t="inlineStr">
         <is>
           <t>weed_type</t>
         </is>
       </c>
-      <c r="B98" s="29" t="inlineStr">
+      <c r="B98" t="inlineStr">
         <is>
           <t>aquatic</t>
         </is>
       </c>
-      <c r="C98" s="29" t="inlineStr">
+      <c r="C98" t="inlineStr">
         <is>
           <t>Aquatic</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="29" t="inlineStr">
+      <c r="A99" t="inlineStr">
         <is>
           <t>weed_type</t>
         </is>
       </c>
-      <c r="B99" s="29" t="inlineStr">
+      <c r="B99" t="inlineStr">
         <is>
           <t>terrestrial</t>
         </is>
       </c>
-      <c r="C99" s="29" t="inlineStr">
+      <c r="C99" t="inlineStr">
         <is>
           <t>Terrestrial</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="29" t="inlineStr">
+      <c r="A100" t="inlineStr">
         <is>
           <t>weed_type</t>
         </is>
       </c>
-      <c r="B100" s="29" t="inlineStr">
+      <c r="B100" t="inlineStr">
         <is>
           <t>parasitic</t>
         </is>
       </c>
-      <c r="C100" s="29" t="inlineStr">
+      <c r="C100" t="inlineStr">
         <is>
           <t>Parasitic</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="29" t="inlineStr">
+      <c r="A101" t="inlineStr">
         <is>
           <t>weed_type</t>
         </is>
       </c>
-      <c r="B101" s="29" t="inlineStr">
+      <c r="B101" t="inlineStr">
         <is>
           <t>epiphytic</t>
         </is>
       </c>
-      <c r="C101" s="29" t="inlineStr">
+      <c r="C101" t="inlineStr">
         <is>
           <t>Epiphytic</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="29" t="inlineStr">
+      <c r="A102" t="inlineStr">
         <is>
           <t>weed_type</t>
         </is>
       </c>
-      <c r="B102" s="29" t="inlineStr">
+      <c r="B102" t="inlineStr">
         <is>
           <t>noxious</t>
         </is>
       </c>
-      <c r="C102" s="29" t="inlineStr">
+      <c r="C102" t="inlineStr">
         <is>
           <t>Noxious</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="29" t="inlineStr">
+      <c r="A103" t="inlineStr">
         <is>
           <t>weed_type</t>
         </is>
       </c>
-      <c r="B103" s="29" t="inlineStr">
+      <c r="B103" t="inlineStr">
         <is>
           <t>poisonous</t>
         </is>
       </c>
-      <c r="C103" s="29" t="inlineStr">
+      <c r="C103" t="inlineStr">
         <is>
           <t>Poisonous</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="29" t="inlineStr">
+      <c r="A104" t="inlineStr">
         <is>
           <t>weed_type</t>
         </is>
       </c>
-      <c r="B104" s="29" t="inlineStr">
+      <c r="B104" t="inlineStr">
         <is>
           <t>allelopathic</t>
         </is>
       </c>
-      <c r="C104" s="29" t="inlineStr">
+      <c r="C104" t="inlineStr">
         <is>
           <t>Allelopathic</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="29" t="inlineStr">
+      <c r="A105" t="inlineStr">
         <is>
           <t>weed_type</t>
         </is>
       </c>
-      <c r="B105" s="29" t="inlineStr">
+      <c r="B105" t="inlineStr">
         <is>
           <t>invasive</t>
         </is>
       </c>
-      <c r="C105" s="29" t="inlineStr">
+      <c r="C105" t="inlineStr">
         <is>
           <t>Invasive</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="29" t="inlineStr">
+      <c r="A106" t="inlineStr">
         <is>
           <t>weed_type</t>
         </is>
       </c>
-      <c r="B106" s="29" t="inlineStr">
+      <c r="B106" t="inlineStr">
         <is>
           <t>climbing</t>
         </is>
       </c>
-      <c r="C106" s="29" t="inlineStr">
+      <c r="C106" t="inlineStr">
         <is>
           <t>Climbing</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="29" t="inlineStr">
+      <c r="A107" t="inlineStr">
         <is>
           <t>weed_type</t>
         </is>
       </c>
-      <c r="B107" s="29" t="inlineStr">
+      <c r="B107" t="inlineStr">
         <is>
           <t>rosette</t>
         </is>
       </c>
-      <c r="C107" s="29" t="inlineStr">
+      <c r="C107" t="inlineStr">
         <is>
           <t>Rosette</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="29" t="inlineStr">
+      <c r="A108" t="inlineStr">
         <is>
           <t>weed_type</t>
         </is>
       </c>
-      <c r="B108" s="29" t="inlineStr">
+      <c r="B108" t="inlineStr">
         <is>
           <t>creeping</t>
         </is>
       </c>
-      <c r="C108" s="29" t="inlineStr">
+      <c r="C108" t="inlineStr">
         <is>
           <t>Creeping</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="29" t="inlineStr">
+      <c r="A109" t="inlineStr">
         <is>
           <t>fertilizer_type</t>
         </is>
       </c>
-      <c r="B109" s="29" t="inlineStr">
+      <c r="B109" t="inlineStr">
         <is>
           <t>nps</t>
         </is>
       </c>
-      <c r="C109" s="29" t="inlineStr">
+      <c r="C109" t="inlineStr">
         <is>
           <t>NPS</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="29" t="inlineStr">
+      <c r="A110" t="inlineStr">
         <is>
           <t>fertilizer_type</t>
         </is>
       </c>
-      <c r="B110" s="29" t="inlineStr">
+      <c r="B110" t="inlineStr">
         <is>
           <t>npsb</t>
         </is>
       </c>
-      <c r="C110" s="29" t="inlineStr">
+      <c r="C110" t="inlineStr">
         <is>
           <t>NPSB</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="29" t="inlineStr">
+      <c r="A111" t="inlineStr">
         <is>
           <t>fertilizer_type</t>
         </is>
       </c>
-      <c r="B111" s="29" t="inlineStr">
+      <c r="B111" t="inlineStr">
         <is>
           <t>dap</t>
         </is>
       </c>
-      <c r="C111" s="29" t="inlineStr">
+      <c r="C111" t="inlineStr">
         <is>
           <t>DAP</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="29" t="inlineStr">
+      <c r="A112" t="inlineStr">
         <is>
           <t>fertilizer_type</t>
         </is>
       </c>
-      <c r="B112" s="29" t="inlineStr">
+      <c r="B112" t="inlineStr">
         <is>
           <t>compost</t>
         </is>
       </c>
-      <c r="C112" s="29" t="inlineStr">
+      <c r="C112" t="inlineStr">
         <is>
           <t>Compost</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="29" t="inlineStr">
+      <c r="A113" t="inlineStr">
         <is>
           <t>fertilizer_type</t>
         </is>
       </c>
-      <c r="B113" s="29" t="inlineStr">
+      <c r="B113" t="inlineStr">
         <is>
           <t>manure</t>
         </is>
       </c>
-      <c r="C113" s="29" t="inlineStr">
+      <c r="C113" t="inlineStr">
         <is>
           <t>Manure</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="29" t="inlineStr">
+      <c r="A114" t="inlineStr">
         <is>
           <t>fertilizer_type</t>
         </is>
       </c>
-      <c r="B114" s="29" t="inlineStr">
+      <c r="B114" t="inlineStr">
         <is>
           <t>blended</t>
         </is>
       </c>
-      <c r="C114" s="29" t="inlineStr">
+      <c r="C114" t="inlineStr">
         <is>
           <t>Blended</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="29" t="inlineStr">
+      <c r="A115" t="inlineStr">
         <is>
           <t>fertilizer_type</t>
         </is>
       </c>
-      <c r="B115" s="29" t="inlineStr">
+      <c r="B115" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="C115" s="29" t="inlineStr">
+      <c r="C115" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="29" t="inlineStr">
+      <c r="A116" t="inlineStr">
         <is>
           <t>sowing_status</t>
         </is>
       </c>
-      <c r="B116" s="29" t="inlineStr">
+      <c r="B116" t="inlineStr">
         <is>
           <t>sown</t>
         </is>
       </c>
-      <c r="C116" s="29" t="inlineStr">
+      <c r="C116" t="inlineStr">
         <is>
           <t>Sown</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="29" t="inlineStr">
+      <c r="A117" t="inlineStr">
         <is>
           <t>sowing_status</t>
         </is>
       </c>
-      <c r="B117" s="29" t="inlineStr">
+      <c r="B117" t="inlineStr">
         <is>
           <t>not_sown</t>
         </is>
       </c>
-      <c r="C117" s="29" t="inlineStr">
+      <c r="C117" t="inlineStr">
         <is>
           <t>Not Sown</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="29" t="inlineStr">
+      <c r="A118" t="inlineStr">
         <is>
           <t>cluster_status</t>
         </is>
       </c>
-      <c r="B118" s="29" t="inlineStr">
+      <c r="B118" t="inlineStr">
         <is>
           <t>clustered</t>
         </is>
       </c>
-      <c r="C118" s="29" t="inlineStr">
+      <c r="C118" t="inlineStr">
         <is>
           <t>Clustered</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="29" t="inlineStr">
+      <c r="A119" t="inlineStr">
         <is>
           <t>cluster_status</t>
         </is>
       </c>
-      <c r="B119" s="29" t="inlineStr">
+      <c r="B119" t="inlineStr">
         <is>
           <t>independent</t>
         </is>
       </c>
-      <c r="C119" s="29" t="inlineStr">
+      <c r="C119" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="29" t="inlineStr">
+      <c r="A120" t="inlineStr">
         <is>
           <t>disease_type</t>
         </is>
       </c>
-      <c r="B120" s="29" t="inlineStr">
+      <c r="B120" t="inlineStr">
         <is>
           <t>leaf_spot</t>
         </is>
       </c>
-      <c r="C120" s="29" t="inlineStr">
+      <c r="C120" t="inlineStr">
         <is>
           <t>Leaf spot</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="29" t="inlineStr">
+      <c r="A121" t="inlineStr">
         <is>
           <t>disease_type</t>
         </is>
       </c>
-      <c r="B121" s="29" t="inlineStr">
+      <c r="B121" t="inlineStr">
         <is>
           <t>powdery_mildew</t>
         </is>
       </c>
-      <c r="C121" s="29" t="inlineStr">
+      <c r="C121" t="inlineStr">
         <is>
           <t>Powdery mildew</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="29" t="inlineStr">
+      <c r="A122" t="inlineStr">
         <is>
           <t>disease_type</t>
         </is>
       </c>
-      <c r="B122" s="29" t="inlineStr">
+      <c r="B122" t="inlineStr">
         <is>
           <t>downy_mildew</t>
         </is>
       </c>
-      <c r="C122" s="29" t="inlineStr">
+      <c r="C122" t="inlineStr">
         <is>
           <t>Downy mildew</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="29" t="inlineStr">
+      <c r="A123" t="inlineStr">
         <is>
           <t>disease_type</t>
         </is>
       </c>
-      <c r="B123" s="29" t="inlineStr">
+      <c r="B123" t="inlineStr">
         <is>
           <t>rust</t>
         </is>
       </c>
-      <c r="C123" s="29" t="inlineStr">
+      <c r="C123" t="inlineStr">
         <is>
           <t>Rust</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="29" t="inlineStr">
+      <c r="A124" t="inlineStr">
         <is>
           <t>disease_type</t>
         </is>
       </c>
-      <c r="B124" s="29" t="inlineStr">
+      <c r="B124" t="inlineStr">
         <is>
           <t>blight</t>
         </is>
       </c>
-      <c r="C124" s="29" t="inlineStr">
+      <c r="C124" t="inlineStr">
         <is>
           <t>Blight</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="29" t="inlineStr">
+      <c r="A125" t="inlineStr">
         <is>
           <t>disease_type</t>
         </is>
       </c>
-      <c r="B125" s="29" t="inlineStr">
+      <c r="B125" t="inlineStr">
         <is>
           <t>wilt</t>
         </is>
       </c>
-      <c r="C125" s="29" t="inlineStr">
+      <c r="C125" t="inlineStr">
         <is>
           <t>Wilt</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="29" t="inlineStr">
+      <c r="A126" t="inlineStr">
         <is>
           <t>disease_type</t>
         </is>
       </c>
-      <c r="B126" s="29" t="inlineStr">
+      <c r="B126" t="inlineStr">
         <is>
           <t>mosaic_virus</t>
         </is>
       </c>
-      <c r="C126" s="29" t="inlineStr">
+      <c r="C126" t="inlineStr">
         <is>
           <t>Mosaic virus</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="29" t="inlineStr">
+      <c r="A127" t="inlineStr">
         <is>
           <t>disease_type</t>
         </is>
       </c>
-      <c r="B127" s="29" t="inlineStr">
+      <c r="B127" t="inlineStr">
         <is>
           <t>smut</t>
         </is>
       </c>
-      <c r="C127" s="29" t="inlineStr">
+      <c r="C127" t="inlineStr">
         <is>
           <t>Smut</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="29" t="inlineStr">
+      <c r="A128" t="inlineStr">
         <is>
           <t>disease_type</t>
         </is>
       </c>
-      <c r="B128" s="29" t="inlineStr">
+      <c r="B128" t="inlineStr">
         <is>
           <t>anthracnose</t>
         </is>
       </c>
-      <c r="C128" s="29" t="inlineStr">
+      <c r="C128" t="inlineStr">
         <is>
           <t>Anthracnose</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="29" t="inlineStr">
+      <c r="A129" t="inlineStr">
         <is>
           <t>disease_type</t>
         </is>
       </c>
-      <c r="B129" s="29" t="inlineStr">
+      <c r="B129" t="inlineStr">
         <is>
           <t>root_rot</t>
         </is>
       </c>
-      <c r="C129" s="29" t="inlineStr">
+      <c r="C129" t="inlineStr">
         <is>
           <t>Root rot</t>
         </is>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="29" t="inlineStr">
+      <c r="A130" t="inlineStr">
         <is>
           <t>fungicide_type</t>
         </is>
       </c>
-      <c r="B130" s="29" t="inlineStr">
+      <c r="B130" t="inlineStr">
         <is>
           <t>fungicide</t>
         </is>
       </c>
-      <c r="C130" s="29" t="inlineStr">
+      <c r="C130" t="inlineStr">
         <is>
           <t>Fungicide</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="29" t="inlineStr">
+      <c r="A131" t="inlineStr">
         <is>
           <t>fungicide_type</t>
         </is>
       </c>
-      <c r="B131" s="29" t="inlineStr">
+      <c r="B131" t="inlineStr">
         <is>
           <t>bactericide</t>
         </is>
       </c>
-      <c r="C131" s="29" t="inlineStr">
+      <c r="C131" t="inlineStr">
         <is>
           <t>Bactericide</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="29" t="inlineStr">
+      <c r="A132" t="inlineStr">
         <is>
           <t>crop_season</t>
         </is>
       </c>
-      <c r="B132" s="29" t="inlineStr">
+      <c r="B132" t="inlineStr">
         <is>
           <t>SEASON_MEHER</t>
         </is>
       </c>
-      <c r="C132" s="29" t="inlineStr">
+      <c r="C132" t="inlineStr">
         <is>
           <t>Meher (main rains)</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="29" t="inlineStr">
+      <c r="A133" t="inlineStr">
         <is>
           <t>crop_season</t>
         </is>
       </c>
-      <c r="B133" s="29" t="inlineStr">
+      <c r="B133" t="inlineStr">
         <is>
           <t>SEASON_BELG</t>
         </is>
       </c>
-      <c r="C133" s="29" t="inlineStr">
+      <c r="C133" t="inlineStr">
         <is>
           <t>Belg (short rains)</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="29" t="inlineStr">
+      <c r="A134" t="inlineStr">
         <is>
           <t>crop_season</t>
         </is>
       </c>
-      <c r="B134" s="29" t="inlineStr">
+      <c r="B134" t="inlineStr">
         <is>
           <t>SEASON_IRRIGATION</t>
         </is>
       </c>
-      <c r="C134" s="29" t="inlineStr">
+      <c r="C134" t="inlineStr">
         <is>
           <t>Irrigation (dry season)</t>
         </is>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="29" t="inlineStr">
+      <c r="A135" t="inlineStr">
         <is>
           <t>agro_ecological_zone</t>
         </is>
       </c>
-      <c r="B135" s="29" t="inlineStr">
+      <c r="B135" t="inlineStr">
         <is>
           <t>AEZ_BEREHA</t>
         </is>
       </c>
-      <c r="C135" s="29" t="inlineStr">
+      <c r="C135" t="inlineStr">
         <is>
           <t>Bereha (hot lowland)</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="29" t="inlineStr">
+      <c r="A136" t="inlineStr">
         <is>
           <t>agro_ecological_zone</t>
         </is>
       </c>
-      <c r="B136" s="29" t="inlineStr">
+      <c r="B136" t="inlineStr">
         <is>
           <t>AEZ_KOLLA</t>
         </is>
       </c>
-      <c r="C136" s="29" t="inlineStr">
+      <c r="C136" t="inlineStr">
         <is>
           <t>Kolla (lowland)</t>
         </is>
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="29" t="inlineStr">
+      <c r="A137" t="inlineStr">
         <is>
           <t>agro_ecological_zone</t>
         </is>
       </c>
-      <c r="B137" s="29" t="inlineStr">
+      <c r="B137" t="inlineStr">
         <is>
           <t>AEZ_WEYNA_DEGA</t>
         </is>
       </c>
-      <c r="C137" s="29" t="inlineStr">
+      <c r="C137" t="inlineStr">
         <is>
           <t>Weyna Dega (midland)</t>
         </is>
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="29" t="inlineStr">
+      <c r="A138" t="inlineStr">
         <is>
           <t>agro_ecological_zone</t>
         </is>
       </c>
-      <c r="B138" s="29" t="inlineStr">
+      <c r="B138" t="inlineStr">
         <is>
           <t>AEZ_DEGA</t>
         </is>
       </c>
-      <c r="C138" s="29" t="inlineStr">
+      <c r="C138" t="inlineStr">
         <is>
           <t>Dega (highland)</t>
         </is>
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="29" t="inlineStr">
+      <c r="A139" t="inlineStr">
         <is>
           <t>agro_ecological_zone</t>
         </is>
       </c>
-      <c r="B139" s="29" t="inlineStr">
+      <c r="B139" t="inlineStr">
         <is>
           <t>AEZ_WURCH</t>
         </is>
       </c>
-      <c r="C139" s="29" t="inlineStr">
+      <c r="C139" t="inlineStr">
         <is>
           <t>Wurch (cold highland)</t>
         </is>
@@ -4813,64 +4813,64 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="29" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>form_title</t>
         </is>
       </c>
-      <c r="B1" s="29" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>form_id</t>
         </is>
       </c>
-      <c r="C1" s="29" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>version</t>
         </is>
       </c>
-      <c r="D1" s="29" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>default_language</t>
         </is>
       </c>
-      <c r="E1" s="29" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>style</t>
         </is>
       </c>
-      <c r="F1" s="29" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>allow_choice_duplicates</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="29" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Crop Sown Registry - 3. Sowing</t>
         </is>
       </c>
-      <c r="B2" s="29" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>crop_sown_registry_sown</t>
         </is>
       </c>
-      <c r="C2" s="29" t="inlineStr">
-        <is>
-          <t>2026.10.31.1</t>
-        </is>
-      </c>
-      <c r="D2" s="29" t="inlineStr">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026.10.31.2</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
         <is>
           <t>English (en)</t>
         </is>
       </c>
-      <c r="E2" s="29" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>pages</t>
         </is>
       </c>
-      <c r="F2" s="29" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
